--- a/gstdatabase/GSTR-3B-2024-2025.xlsx
+++ b/gstdatabase/GSTR-3B-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7528456A-D3E5-40A0-A548-0BD785C6E894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEBD732-5938-40DD-98B2-9A764CBFDFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15644</v>
+        <v>15649</v>
       </c>
       <c r="F10" s="13">
-        <v>73034</v>
+        <v>73039</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0017007269236045</v>
+        <v>1.001769304622137</v>
       </c>
       <c r="H10" s="7">
         <v>74548</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>15558</v>
+        <v>15562</v>
       </c>
       <c r="K10" s="13">
-        <v>74114</v>
+        <v>74118</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.9941782475720341</v>
+        <v>0.99423190427643937</v>
       </c>
       <c r="M10" s="7">
         <v>129395</v>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>25088</v>
+        <v>25093</v>
       </c>
       <c r="P10" s="6">
-        <v>129065</v>
+        <v>129070</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99744966961629122</v>
+        <v>0.99748831098574131</v>
       </c>
       <c r="R10" s="7">
         <v>72583</v>
@@ -1530,14 +1530,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>14238</v>
+        <v>14246</v>
       </c>
       <c r="U10" s="13">
-        <v>73066</v>
+        <v>73074</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.0066544507667086</v>
+        <v>1.006764669412948</v>
       </c>
       <c r="W10" s="7">
         <v>74384</v>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>15712</v>
+        <v>15719</v>
       </c>
       <c r="Z10" s="13">
-        <v>73669</v>
+        <v>73676</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99038771778877177</v>
+        <v>0.99048182404818241</v>
       </c>
       <c r="AB10" s="7">
         <v>130621</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>26375</v>
+        <v>26386</v>
       </c>
       <c r="AE10" s="6">
-        <v>129928</v>
+        <v>129939</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99469457437931119</v>
+        <v>0.99477878748440141</v>
       </c>
       <c r="AG10" s="7">
         <v>72721</v>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14499</v>
+        <v>14509</v>
       </c>
       <c r="AJ10" s="6">
-        <v>72713</v>
+        <v>72723</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99988999051168159</v>
+        <v>1.0000275023720795</v>
       </c>
       <c r="AL10" s="7">
         <v>74187</v>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>13080</v>
+        <v>13092</v>
       </c>
       <c r="AO10" s="6">
-        <v>73765</v>
+        <v>73777</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99431167185625513</v>
+        <v>0.99447342526318627</v>
       </c>
       <c r="AQ10" s="7">
         <v>132270</v>
@@ -1615,14 +1615,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>21559</v>
+        <v>21578</v>
       </c>
       <c r="AT10" s="6">
-        <v>132039</v>
+        <v>132058</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.99825357223860289</v>
+        <v>0.99839721781205115</v>
       </c>
       <c r="AV10" s="7">
         <v>73561</v>
@@ -1632,14 +1632,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>12845</v>
+        <v>12861</v>
       </c>
       <c r="AY10" s="6">
-        <v>73594</v>
+        <v>73610</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>1.0004486072783132</v>
+        <v>1.0006661138374955</v>
       </c>
       <c r="BA10" s="7">
         <v>75582</v>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>12533</v>
+        <v>12546</v>
       </c>
       <c r="BD10" s="6">
-        <v>74498</v>
+        <v>74511</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.985657960890159</v>
+        <v>0.98582995951417007</v>
       </c>
       <c r="BF10" s="7">
         <v>134150</v>
@@ -1666,14 +1666,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>33091</v>
+        <v>33119</v>
       </c>
       <c r="BI10" s="6">
-        <v>133558</v>
+        <v>133586</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99558702944465149</v>
+        <v>0.99579575102497209</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8254</v>
+        <v>8258</v>
       </c>
       <c r="F11" s="13">
-        <v>46492</v>
+        <v>46496</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99894716486538748</v>
+        <v>0.99903311059066202</v>
       </c>
       <c r="H11" s="7">
         <v>47616</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8152</v>
+        <v>8155</v>
       </c>
       <c r="K11" s="13">
-        <v>47149</v>
+        <v>47152</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.990192372311828</v>
+        <v>0.990255376344086</v>
       </c>
       <c r="M11" s="7">
         <v>108402</v>
@@ -1725,14 +1725,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>16835</v>
+        <v>16845</v>
       </c>
       <c r="P11" s="6">
-        <v>107793</v>
+        <v>107803</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.9943820224719101</v>
+        <v>0.99447427169240421</v>
       </c>
       <c r="R11" s="7">
         <v>46539</v>
@@ -1742,14 +1742,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8208</v>
+        <v>8215</v>
       </c>
       <c r="U11" s="13">
-        <v>46476</v>
+        <v>46483</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99864629665441884</v>
+        <v>0.99879670813726118</v>
       </c>
       <c r="W11" s="7">
         <v>48300</v>
@@ -1759,14 +1759,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8384</v>
+        <v>8390</v>
       </c>
       <c r="Z11" s="13">
-        <v>47089</v>
+        <v>47095</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97492753623188411</v>
+        <v>0.97505175983436854</v>
       </c>
       <c r="AB11" s="7">
         <v>109219</v>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>18162</v>
+        <v>18173</v>
       </c>
       <c r="AE11" s="6">
-        <v>108444</v>
+        <v>108455</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99290416502623169</v>
+        <v>0.9930048801032787</v>
       </c>
       <c r="AG11" s="7">
         <v>46763</v>
@@ -1793,14 +1793,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI47" si="12">AJ11-AH11</f>
-        <v>8333</v>
+        <v>8339</v>
       </c>
       <c r="AJ11" s="6">
-        <v>46702</v>
+        <v>46708</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99869554990056242</v>
+        <v>0.99882385646772021</v>
       </c>
       <c r="AL11" s="7">
         <v>48206</v>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7540</v>
+        <v>7544</v>
       </c>
       <c r="AO11" s="6">
-        <v>47229</v>
+        <v>47233</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97973281334273743</v>
+        <v>0.97981579056548973</v>
       </c>
       <c r="AQ11" s="7">
         <v>110196</v>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15129</v>
+        <v>15144</v>
       </c>
       <c r="AT11" s="6">
-        <v>109682</v>
+        <v>109697</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99533558386874299</v>
+        <v>0.99547170496206761</v>
       </c>
       <c r="AV11" s="7">
         <v>47206</v>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7589</v>
+        <v>7594</v>
       </c>
       <c r="AY11" s="6">
-        <v>47045</v>
+        <v>47050</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99658941659958478</v>
+        <v>0.99669533533872812</v>
       </c>
       <c r="BA11" s="7">
         <v>48813</v>
@@ -1861,14 +1861,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7449</v>
+        <v>7456</v>
       </c>
       <c r="BD11" s="6">
-        <v>47572</v>
+        <v>47579</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97457644479954109</v>
+        <v>0.97471984922049459</v>
       </c>
       <c r="BF11" s="7">
         <v>111276</v>
@@ -1878,14 +1878,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>21116</v>
+        <v>21139</v>
       </c>
       <c r="BI11" s="6">
-        <v>110665</v>
+        <v>110688</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99450914842373916</v>
+        <v>0.99471584169093064</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>27465</v>
+        <v>27470</v>
       </c>
       <c r="F12" s="13">
-        <v>175790</v>
+        <v>175795</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99265349453106033</v>
+        <v>0.99268172860280868</v>
       </c>
       <c r="H12" s="7">
         <v>181172</v>
@@ -1920,14 +1920,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>25324</v>
+        <v>25331</v>
       </c>
       <c r="K12" s="13">
-        <v>178150</v>
+        <v>178157</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98331971827876274</v>
+        <v>0.98335835559578744</v>
       </c>
       <c r="M12" s="7">
         <v>363483</v>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>56219</v>
+        <v>56228</v>
       </c>
       <c r="P12" s="6">
-        <v>360453</v>
+        <v>360462</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99166398428537239</v>
+        <v>0.9916887447280891</v>
       </c>
       <c r="R12" s="7">
         <v>177513</v>
@@ -1954,14 +1954,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27063</v>
+        <v>27072</v>
       </c>
       <c r="U12" s="13">
-        <v>177183</v>
+        <v>177192</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99814098122391037</v>
+        <v>0.99819168173598549</v>
       </c>
       <c r="W12" s="7">
         <v>182324</v>
@@ -1971,14 +1971,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>28731</v>
+        <v>28740</v>
       </c>
       <c r="Z12" s="13">
-        <v>178803</v>
+        <v>178812</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98068822535705669</v>
+        <v>0.98073758803010025</v>
       </c>
       <c r="AB12" s="7">
         <v>365690</v>
@@ -1988,14 +1988,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>60872</v>
+        <v>60884</v>
       </c>
       <c r="AE12" s="6">
-        <v>362435</v>
+        <v>362447</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99109901829418356</v>
+        <v>0.99113183297328333</v>
       </c>
       <c r="AG12" s="7">
         <v>180670</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>30071</v>
+        <v>30081</v>
       </c>
       <c r="AJ12" s="6">
-        <v>178448</v>
+        <v>178458</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.98770133392372839</v>
+        <v>0.98775668345602474</v>
       </c>
       <c r="AL12" s="7">
         <v>181581</v>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25729</v>
+        <v>25739</v>
       </c>
       <c r="AO12" s="6">
-        <v>178592</v>
+        <v>178602</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98353902666027837</v>
+        <v>0.98359409850149515</v>
       </c>
       <c r="AQ12" s="7">
         <v>363376</v>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>54229</v>
+        <v>54252</v>
       </c>
       <c r="AT12" s="6">
-        <v>362109</v>
+        <v>362132</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99651325348949849</v>
+        <v>0.99657654880894719</v>
       </c>
       <c r="AV12" s="7">
         <v>179534</v>
@@ -2056,14 +2056,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>26132</v>
+        <v>26148</v>
       </c>
       <c r="AY12" s="6">
-        <v>178852</v>
+        <v>178868</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.9962012766384083</v>
+        <v>0.99629039624806448</v>
       </c>
       <c r="BA12" s="7">
         <v>184469</v>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>26328</v>
+        <v>26344</v>
       </c>
       <c r="BD12" s="6">
-        <v>181905</v>
+        <v>181921</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98610064563693633</v>
+        <v>0.98618738107757942</v>
       </c>
       <c r="BF12" s="7">
         <v>368393</v>
@@ -2090,14 +2090,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>77178</v>
+        <v>77210</v>
       </c>
       <c r="BI12" s="6">
-        <v>367141</v>
+        <v>367173</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99660145551082679</v>
+        <v>0.99668831926773849</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2115,14 +2115,14 @@
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="F13" s="13">
-        <v>17583</v>
+        <v>17584</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>1.0021658592191507</v>
+        <v>1.0022228555143915</v>
       </c>
       <c r="H13" s="7">
         <v>181172</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="K13" s="13">
-        <v>17677</v>
+        <v>17678</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>9.7570264720817784E-2</v>
+        <v>9.7575784337535595E-2</v>
       </c>
       <c r="M13" s="7">
         <v>28677</v>
@@ -2149,14 +2149,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>4348</v>
+        <v>4349</v>
       </c>
       <c r="P13" s="6">
-        <v>28637</v>
+        <v>28638</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99860515395613214</v>
+        <v>0.99864002510722882</v>
       </c>
       <c r="R13" s="7">
         <v>17606</v>
@@ -2166,14 +2166,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="U13" s="13">
-        <v>17619</v>
+        <v>17620</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>1.0007383846415994</v>
+        <v>1.000795183460184</v>
       </c>
       <c r="W13" s="7">
         <v>17849</v>
@@ -2183,14 +2183,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="Z13" s="13">
-        <v>17748</v>
+        <v>17749</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.99434141968737744</v>
+        <v>0.99439744523502716</v>
       </c>
       <c r="AB13" s="7">
         <v>28890</v>
@@ -2200,14 +2200,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4669</v>
+        <v>4670</v>
       </c>
       <c r="AE13" s="6">
-        <v>28822</v>
+        <v>28823</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.99764624437521632</v>
+        <v>0.99768085842852194</v>
       </c>
       <c r="AG13" s="7">
         <v>17747</v>
@@ -2217,14 +2217,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="AJ13" s="6">
-        <v>17838</v>
+        <v>17839</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>1.0051276272045979</v>
+        <v>1.0051839747562969</v>
       </c>
       <c r="AL13" s="7">
         <v>17937</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="AO13" s="6">
-        <v>17868</v>
+        <v>17869</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>0.99615320287673526</v>
+        <v>0.99620895355968109</v>
       </c>
       <c r="AQ13" s="7">
         <v>28933</v>
@@ -2251,14 +2251,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4311</v>
+        <v>4312</v>
       </c>
       <c r="AT13" s="6">
-        <v>28958</v>
+        <v>28959</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.000864065254208</v>
+        <v>1.0008986278643763</v>
       </c>
       <c r="AV13" s="7">
         <v>17858</v>
@@ -2268,14 +2268,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="AY13" s="6">
-        <v>17908</v>
+        <v>17909</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.002799865606451</v>
+        <v>1.00285586291858</v>
       </c>
       <c r="BA13" s="7">
         <v>18026</v>
@@ -2285,14 +2285,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="BD13" s="6">
-        <v>17929</v>
+        <v>17932</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>0.99461888383446129</v>
+        <v>0.99478531010762228</v>
       </c>
       <c r="BF13" s="7">
         <v>29023</v>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>5658</v>
+        <v>5663</v>
       </c>
       <c r="BI13" s="6">
-        <v>29079</v>
+        <v>29084</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.001929504186335</v>
+        <v>1.0021017813458293</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18633</v>
+        <v>18640</v>
       </c>
       <c r="F14" s="13">
-        <v>89943</v>
+        <v>89950</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99419684308263701</v>
+        <v>0.99427421850820175</v>
       </c>
       <c r="H14" s="7">
         <v>94129</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>17777</v>
+        <v>17785</v>
       </c>
       <c r="K14" s="13">
-        <v>91396</v>
+        <v>91404</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.97096537730136301</v>
+        <v>0.97105036704947467</v>
       </c>
       <c r="M14" s="7">
         <v>164995</v>
@@ -2361,14 +2361,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31710</v>
+        <v>31725</v>
       </c>
       <c r="P14" s="6">
-        <v>163675</v>
+        <v>163690</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99199975756841119</v>
+        <v>0.99209066941422464</v>
       </c>
       <c r="R14" s="7">
         <v>91074</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18928</v>
+        <v>18938</v>
       </c>
       <c r="U14" s="13">
-        <v>90866</v>
+        <v>90876</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99771614291674904</v>
+        <v>0.99782594373805911</v>
       </c>
       <c r="W14" s="7">
         <v>93800</v>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>18593</v>
+        <v>18607</v>
       </c>
       <c r="Z14" s="13">
-        <v>91376</v>
+        <v>91390</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.9741577825159915</v>
+        <v>0.97430703624733472</v>
       </c>
       <c r="AB14" s="7">
         <v>166352</v>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34998</v>
+        <v>35020</v>
       </c>
       <c r="AE14" s="6">
-        <v>164441</v>
+        <v>164463</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.98851231124362793</v>
+        <v>0.98864456093103781</v>
       </c>
       <c r="AG14" s="7">
         <v>92175</v>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19153</v>
+        <v>19168</v>
       </c>
       <c r="AJ14" s="6">
-        <v>91600</v>
+        <v>91615</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99376186601573091</v>
+        <v>0.99392459994575533</v>
       </c>
       <c r="AL14" s="7">
         <v>94655</v>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17447</v>
+        <v>17461</v>
       </c>
       <c r="AO14" s="6">
-        <v>93030</v>
+        <v>93044</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98283239131583122</v>
+        <v>0.98298029686757171</v>
       </c>
       <c r="AQ14" s="7">
         <v>168400</v>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>31389</v>
+        <v>31411</v>
       </c>
       <c r="AT14" s="6">
-        <v>167431</v>
+        <v>167453</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99424584323040377</v>
+        <v>0.99437648456057004</v>
       </c>
       <c r="AV14" s="7">
         <v>94024</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>16988</v>
+        <v>17002</v>
       </c>
       <c r="AY14" s="6">
-        <v>93576</v>
+        <v>93590</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.99523525908278743</v>
+        <v>0.99538415723645024</v>
       </c>
       <c r="BA14" s="7">
         <v>96514</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16751</v>
+        <v>16772</v>
       </c>
       <c r="BD14" s="6">
-        <v>94979</v>
+        <v>95000</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98409557162691419</v>
+        <v>0.98431315664048735</v>
       </c>
       <c r="BF14" s="7">
         <v>171502</v>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39868</v>
+        <v>39905</v>
       </c>
       <c r="BI14" s="6">
-        <v>170669</v>
+        <v>170706</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99514291378526198</v>
+        <v>0.99535865470956608</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>50772</v>
+        <v>50777</v>
       </c>
       <c r="F15" s="13">
-        <v>301918</v>
+        <v>301923</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99135448578399021</v>
+        <v>0.99137090339549039</v>
       </c>
       <c r="H15" s="7">
         <v>309950</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47831</v>
+        <v>47834</v>
       </c>
       <c r="K15" s="13">
-        <v>306464</v>
+        <v>306467</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98875302468140025</v>
+        <v>0.9887627036618809</v>
       </c>
       <c r="M15" s="7">
         <v>517862</v>
@@ -2573,14 +2573,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81205</v>
+        <v>81210</v>
       </c>
       <c r="P15" s="6">
-        <v>512954</v>
+        <v>512959</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.9905225716503625</v>
+        <v>0.99053222673221819</v>
       </c>
       <c r="R15" s="7">
         <v>307768</v>
@@ -2590,14 +2590,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>52562</v>
+        <v>52566</v>
       </c>
       <c r="U15" s="13">
-        <v>306414</v>
+        <v>306418</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99560058225676484</v>
+        <v>0.99561357905955139</v>
       </c>
       <c r="W15" s="7">
         <v>314114</v>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>50998</v>
+        <v>51002</v>
       </c>
       <c r="Z15" s="13">
-        <v>308559</v>
+        <v>308563</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98231533774362179</v>
+        <v>0.9823280719738694</v>
       </c>
       <c r="AB15" s="7">
         <v>523203</v>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>91414</v>
+        <v>91424</v>
       </c>
       <c r="AE15" s="6">
-        <v>519191</v>
+        <v>519201</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99233184825010556</v>
+        <v>0.9923509612903596</v>
       </c>
       <c r="AG15" s="7">
         <v>312916</v>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54281</v>
+        <v>54289</v>
       </c>
       <c r="AJ15" s="6">
-        <v>310821</v>
+        <v>310829</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99330491250047936</v>
+        <v>0.99333047846706468</v>
       </c>
       <c r="AL15" s="7">
         <v>318942</v>
@@ -2658,14 +2658,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>48599</v>
+        <v>48607</v>
       </c>
       <c r="AO15" s="6">
-        <v>313912</v>
+        <v>313920</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98422910748662762</v>
+        <v>0.98425419041706641</v>
       </c>
       <c r="AQ15" s="7">
         <v>530087</v>
@@ -2675,14 +2675,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>77523</v>
+        <v>77539</v>
       </c>
       <c r="AT15" s="6">
-        <v>526562</v>
+        <v>526578</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99335014818322276</v>
+        <v>0.99338033190778119</v>
       </c>
       <c r="AV15" s="7">
         <v>317508</v>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>49783</v>
+        <v>49794</v>
       </c>
       <c r="AY15" s="6">
-        <v>316794</v>
+        <v>316805</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99775123776408781</v>
+        <v>0.99778588256043943</v>
       </c>
       <c r="BA15" s="7">
         <v>324414</v>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>49284</v>
+        <v>49296</v>
       </c>
       <c r="BD15" s="6">
-        <v>320660</v>
+        <v>320672</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98842836622340591</v>
+        <v>0.98846535599573382</v>
       </c>
       <c r="BF15" s="7">
         <v>538701</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>107891</v>
+        <v>107921</v>
       </c>
       <c r="BI15" s="6">
-        <v>536174</v>
+        <v>536204</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99530908611641711</v>
+        <v>0.9953647756362064</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>75616</v>
+        <v>75630</v>
       </c>
       <c r="F16" s="13">
-        <v>440531</v>
+        <v>440545</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.98845130340739273</v>
+        <v>0.98848271622112827</v>
       </c>
       <c r="H16" s="7">
         <v>453561</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>72386</v>
+        <v>72402</v>
       </c>
       <c r="K16" s="13">
-        <v>444609</v>
+        <v>444625</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98026285328765039</v>
+        <v>0.98029812968928109</v>
       </c>
       <c r="M16" s="7">
         <v>776551</v>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>126693</v>
+        <v>126734</v>
       </c>
       <c r="P16" s="6">
-        <v>768677</v>
+        <v>768718</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.98986029249849661</v>
+        <v>0.98991309006105199</v>
       </c>
       <c r="R16" s="7">
         <v>446959</v>
@@ -2802,14 +2802,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>79302</v>
+        <v>79324</v>
       </c>
       <c r="U16" s="13">
-        <v>443787</v>
+        <v>443809</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.99290315219069314</v>
+        <v>0.99295237370765554</v>
       </c>
       <c r="W16" s="7">
         <v>453618</v>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73820</v>
+        <v>73843</v>
       </c>
       <c r="Z16" s="13">
-        <v>443167</v>
+        <v>443190</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.97696079079754328</v>
+        <v>0.97701149425287359</v>
       </c>
       <c r="AB16" s="7">
         <v>775718</v>
@@ -2836,14 +2836,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135787</v>
+        <v>135853</v>
       </c>
       <c r="AE16" s="6">
-        <v>767475</v>
+        <v>767541</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.98937371570596533</v>
+        <v>0.98945879817150051</v>
       </c>
       <c r="AG16" s="7">
         <v>444751</v>
@@ -2853,14 +2853,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79561</v>
+        <v>79600</v>
       </c>
       <c r="AJ16" s="6">
-        <v>439599</v>
+        <v>439638</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98841599007084868</v>
+        <v>0.98850367958700491</v>
       </c>
       <c r="AL16" s="7">
         <v>448369</v>
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70753</v>
+        <v>70796</v>
       </c>
       <c r="AO16" s="6">
-        <v>440160</v>
+        <v>440203</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98169141934433468</v>
+        <v>0.9817873224955338</v>
       </c>
       <c r="AQ16" s="7">
         <v>770483</v>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>116755</v>
+        <v>116849</v>
       </c>
       <c r="AT16" s="6">
-        <v>767094</v>
+        <v>767188</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99560146038264308</v>
+        <v>0.99572346177657389</v>
       </c>
       <c r="AV16" s="7">
         <v>444563</v>
@@ -2904,14 +2904,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>72310</v>
+        <v>72364</v>
       </c>
       <c r="AY16" s="6">
-        <v>444372</v>
+        <v>444426</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.99957036460524151</v>
+        <v>0.99969183220375968</v>
       </c>
       <c r="BA16" s="7">
         <v>453397</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>71562</v>
+        <v>71614</v>
       </c>
       <c r="BD16" s="6">
-        <v>448019</v>
+        <v>448071</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98813843055864947</v>
+        <v>0.9882531203338355</v>
       </c>
       <c r="BF16" s="7">
         <v>780218</v>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>151137</v>
+        <v>151270</v>
       </c>
       <c r="BI16" s="6">
-        <v>777115</v>
+        <v>777248</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99602290641846258</v>
+        <v>0.99619337159614363</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2963,14 +2963,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>54532</v>
+        <v>54544</v>
       </c>
       <c r="F17" s="13">
-        <v>322886</v>
+        <v>322898</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99666939329865878</v>
+        <v>0.99670643433704253</v>
       </c>
       <c r="H17" s="7">
         <v>333085</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>50254</v>
+        <v>50267</v>
       </c>
       <c r="K17" s="13">
-        <v>329483</v>
+        <v>329496</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98918594352792832</v>
+        <v>0.98922497260459041</v>
       </c>
       <c r="M17" s="7">
         <v>731481</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>121323</v>
+        <v>121351</v>
       </c>
       <c r="P17" s="6">
-        <v>727004</v>
+        <v>727032</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99387954027514047</v>
+        <v>0.9939178187813491</v>
       </c>
       <c r="R17" s="7">
         <v>324758</v>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>57865</v>
+        <v>57881</v>
       </c>
       <c r="U17" s="13">
-        <v>324976</v>
+        <v>324992</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0006712690680446</v>
+        <v>1.00072053652258</v>
       </c>
       <c r="W17" s="7">
         <v>336053</v>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>57112</v>
+        <v>57133</v>
       </c>
       <c r="Z17" s="13">
-        <v>327998</v>
+        <v>328019</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97603056660705301</v>
+        <v>0.97609305674997693</v>
       </c>
       <c r="AB17" s="7">
         <v>736224</v>
@@ -3048,14 +3048,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>131026</v>
+        <v>131067</v>
       </c>
       <c r="AE17" s="6">
-        <v>728809</v>
+        <v>728850</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.98992833702786109</v>
+        <v>0.98998402660059981</v>
       </c>
       <c r="AG17" s="7">
         <v>328692</v>
@@ -3065,14 +3065,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>57766</v>
+        <v>57791</v>
       </c>
       <c r="AJ17" s="6">
-        <v>327512</v>
+        <v>327537</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99641001302130872</v>
+        <v>0.99648607206746742</v>
       </c>
       <c r="AL17" s="7">
         <v>339621</v>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51666</v>
+        <v>51692</v>
       </c>
       <c r="AO17" s="6">
-        <v>333272</v>
+        <v>333298</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98130563186610953</v>
+        <v>0.9813821877916854</v>
       </c>
       <c r="AQ17" s="7">
         <v>745574</v>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>114453</v>
+        <v>114519</v>
       </c>
       <c r="AT17" s="6">
-        <v>740248</v>
+        <v>740314</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99285651055428437</v>
+        <v>0.99294503295447534</v>
       </c>
       <c r="AV17" s="7">
         <v>334329</v>
@@ -3116,14 +3116,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>53724</v>
+        <v>53754</v>
       </c>
       <c r="AY17" s="6">
-        <v>333814</v>
+        <v>333844</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.99845960117130128</v>
+        <v>0.99854933314190508</v>
       </c>
       <c r="BA17" s="7">
         <v>348862</v>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>52655</v>
+        <v>52698</v>
       </c>
       <c r="BD17" s="6">
-        <v>340640</v>
+        <v>340683</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.97643194157001911</v>
+        <v>0.97655519947715719</v>
       </c>
       <c r="BF17" s="7">
         <v>757181</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>157515</v>
+        <v>157616</v>
       </c>
       <c r="BI17" s="6">
-        <v>753929</v>
+        <v>754030</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99570512202498473</v>
+        <v>0.99583851153158887</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>184196</v>
+        <v>184231</v>
       </c>
       <c r="F18" s="13">
-        <v>989607</v>
+        <v>989642</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99114128671182988</v>
+        <v>0.99117634097583063</v>
       </c>
       <c r="H18" s="7">
         <v>1018686</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>172477</v>
+        <v>172513</v>
       </c>
       <c r="K18" s="13">
-        <v>1002454</v>
+        <v>1002490</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98406574744327502</v>
+        <v>0.98410108708669797</v>
       </c>
       <c r="M18" s="7">
         <v>1536859</v>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>262175</v>
+        <v>262229</v>
       </c>
       <c r="P18" s="6">
-        <v>1521144</v>
+        <v>1521198</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.98977459871074702</v>
+        <v>0.98980973531078653</v>
       </c>
       <c r="R18" s="7">
         <v>1011292</v>
@@ -3226,14 +3226,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>185880</v>
+        <v>185921</v>
       </c>
       <c r="U18" s="13">
-        <v>1004222</v>
+        <v>1004263</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99300894301546927</v>
+        <v>0.99304948521297509</v>
       </c>
       <c r="W18" s="7">
         <v>1030498</v>
@@ -3243,14 +3243,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>183032</v>
+        <v>183074</v>
       </c>
       <c r="Z18" s="13">
-        <v>1009350</v>
+        <v>1009392</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.97947788350875009</v>
+        <v>0.97951864050197091</v>
       </c>
       <c r="AB18" s="7">
         <v>1557879</v>
@@ -3260,14 +3260,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>285278</v>
+        <v>285363</v>
       </c>
       <c r="AE18" s="6">
-        <v>1537708</v>
+        <v>1537793</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98705226785905709</v>
+        <v>0.98710682922101134</v>
       </c>
       <c r="AG18" s="7">
         <v>1025067</v>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195390</v>
+        <v>195448</v>
       </c>
       <c r="AJ18" s="6">
-        <v>1019044</v>
+        <v>1019102</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99412428651005247</v>
+        <v>0.99418086817739715</v>
       </c>
       <c r="AL18" s="7">
         <v>1045736</v>
@@ -3294,14 +3294,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>168838</v>
+        <v>168905</v>
       </c>
       <c r="AO18" s="6">
-        <v>1032269</v>
+        <v>1032336</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98712198872373147</v>
+        <v>0.98718605843157359</v>
       </c>
       <c r="AQ18" s="7">
         <v>1584961</v>
@@ -3311,14 +3311,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>240718</v>
+        <v>240834</v>
       </c>
       <c r="AT18" s="6">
-        <v>1571127</v>
+        <v>1571243</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99127170952471388</v>
+        <v>0.99134489744542609</v>
       </c>
       <c r="AV18" s="7">
         <v>1051416</v>
@@ -3328,14 +3328,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>177180</v>
+        <v>177255</v>
       </c>
       <c r="AY18" s="6">
-        <v>1046710</v>
+        <v>1046785</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99552413126678685</v>
+        <v>0.99559546364141316</v>
       </c>
       <c r="BA18" s="7">
         <v>1075670</v>
@@ -3345,14 +3345,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>179703</v>
+        <v>179807</v>
       </c>
       <c r="BD18" s="6">
-        <v>1060979</v>
+        <v>1061083</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98634246562607486</v>
+        <v>0.9864391495533017</v>
       </c>
       <c r="BF18" s="7">
         <v>1620029</v>
@@ -3362,14 +3362,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>349986</v>
+        <v>350183</v>
       </c>
       <c r="BI18" s="6">
-        <v>1605514</v>
+        <v>1605711</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99104028384677068</v>
+        <v>0.9911618866082027</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63469</v>
+        <v>63498</v>
       </c>
       <c r="F19" s="13">
-        <v>285043</v>
+        <v>285072</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.97830212963121854</v>
+        <v>0.97840166114667171</v>
       </c>
       <c r="H19" s="7">
         <v>301141</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>54190</v>
+        <v>54219</v>
       </c>
       <c r="K19" s="13">
-        <v>289195</v>
+        <v>289224</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.96033087490577507</v>
+        <v>0.96042717530990462</v>
       </c>
       <c r="M19" s="7">
         <v>505864</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>88490</v>
+        <v>88544</v>
       </c>
       <c r="P19" s="6">
-        <v>496311</v>
+        <v>496365</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.98111547767779483</v>
+        <v>0.98122222573656159</v>
       </c>
       <c r="R19" s="7">
         <v>293000</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>54106</v>
+        <v>54139</v>
       </c>
       <c r="U19" s="13">
-        <v>286838</v>
+        <v>286871</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.9789692832764505</v>
+        <v>0.97908191126279864</v>
       </c>
       <c r="W19" s="7">
         <v>302979</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59711</v>
+        <v>59752</v>
       </c>
       <c r="Z19" s="13">
-        <v>287771</v>
+        <v>287812</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.94980510200376922</v>
+        <v>0.94994042491393793</v>
       </c>
       <c r="AB19" s="7">
         <v>514622</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>103624</v>
+        <v>103703</v>
       </c>
       <c r="AE19" s="6">
-        <v>497257</v>
+        <v>497336</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.96625678653458269</v>
+        <v>0.96641029726673167</v>
       </c>
       <c r="AG19" s="7">
         <v>295766</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>61700</v>
+        <v>61747</v>
       </c>
       <c r="AJ19" s="6">
-        <v>287544</v>
+        <v>287591</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97220099673390448</v>
+        <v>0.97235990614201773</v>
       </c>
       <c r="AL19" s="7">
         <v>302797</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>54656</v>
+        <v>54707</v>
       </c>
       <c r="AO19" s="6">
-        <v>291231</v>
+        <v>291282</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.96180279196953733</v>
+        <v>0.96197122164354332</v>
       </c>
       <c r="AQ19" s="7">
         <v>519490</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>88513</v>
+        <v>88612</v>
       </c>
       <c r="AT19" s="6">
-        <v>506185</v>
+        <v>506284</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.97438834241275096</v>
+        <v>0.97457891393482066</v>
       </c>
       <c r="AV19" s="7">
         <v>299668</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>55977</v>
+        <v>56032</v>
       </c>
       <c r="AY19" s="6">
-        <v>294927</v>
+        <v>294982</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98417915826848379</v>
+        <v>0.9843626947154851</v>
       </c>
       <c r="BA19" s="7">
         <v>313772</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>57921</v>
+        <v>57985</v>
       </c>
       <c r="BD19" s="6">
-        <v>299577</v>
+        <v>299641</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.95476014430860623</v>
+        <v>0.95496411407008908</v>
       </c>
       <c r="BF19" s="7">
         <v>528004</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>133510</v>
+        <v>133652</v>
       </c>
       <c r="BI19" s="6">
-        <v>516917</v>
+        <v>517059</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97900205301474985</v>
+        <v>0.97927099037128507</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="F20" s="13">
-        <v>6423</v>
+        <v>6426</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99396471680594245</v>
+        <v>0.99442896935933145</v>
       </c>
       <c r="H20" s="7">
         <v>6957</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="K20" s="13">
-        <v>6473</v>
+        <v>6476</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.93042978295242207</v>
+        <v>0.93086100330602273</v>
       </c>
       <c r="M20" s="7">
         <v>9947</v>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="P20" s="6">
-        <v>9837</v>
+        <v>9838</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.98894138936362719</v>
+        <v>0.98904192218759424</v>
       </c>
       <c r="R20" s="7">
         <v>6587</v>
@@ -3650,14 +3650,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="U20" s="13">
-        <v>6521</v>
+        <v>6522</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.98998026415667228</v>
+        <v>0.99013207833611661</v>
       </c>
       <c r="W20" s="7">
         <v>6643</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="Z20" s="13">
-        <v>6518</v>
+        <v>6520</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.98118320036128259</v>
+        <v>0.98148426915550202</v>
       </c>
       <c r="AB20" s="7">
         <v>9927</v>
@@ -3684,14 +3684,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="AE20" s="6">
-        <v>9881</v>
+        <v>9883</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.9953661730633625</v>
+        <v>0.99556764379973806</v>
       </c>
       <c r="AG20" s="7">
         <v>6546</v>
@@ -3701,14 +3701,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="AJ20" s="6">
-        <v>6492</v>
+        <v>6493</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.99175068744271311</v>
+        <v>0.99190345249007028</v>
       </c>
       <c r="AL20" s="7">
         <v>6627</v>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="AO20" s="6">
-        <v>6557</v>
+        <v>6558</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.98943715104873997</v>
+        <v>0.98958804889090091</v>
       </c>
       <c r="AQ20" s="7">
         <v>9949</v>
@@ -3735,14 +3735,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="AT20" s="6">
-        <v>9972</v>
+        <v>9974</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0023117901296612</v>
+        <v>1.0025128153583274</v>
       </c>
       <c r="AV20" s="7">
         <v>6437</v>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="AY20" s="6">
-        <v>6444</v>
+        <v>6445</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>1.0010874631039304</v>
+        <v>1.0012428149759205</v>
       </c>
       <c r="BA20" s="7">
         <v>6564</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="BD20" s="6">
-        <v>6521</v>
+        <v>6523</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.9934491163924436</v>
+        <v>0.99375380865326024</v>
       </c>
       <c r="BF20" s="7">
         <v>10109</v>
@@ -3786,14 +3786,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3046</v>
+        <v>3051</v>
       </c>
       <c r="BI20" s="6">
-        <v>10070</v>
+        <v>10075</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.99614205163715497</v>
+        <v>0.99663666040162235</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3811,14 +3811,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4210</v>
+        <v>4216</v>
       </c>
       <c r="F21" s="13">
-        <v>10923</v>
+        <v>10929</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.99417493401292434</v>
+        <v>0.99472103394921274</v>
       </c>
       <c r="H21" s="7">
         <v>10970</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3488</v>
+        <v>3494</v>
       </c>
       <c r="K21" s="13">
-        <v>10965</v>
+        <v>10971</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99954421148587058</v>
+        <v>1.000091157702826</v>
       </c>
       <c r="M21" s="7">
         <v>14288</v>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4662</v>
+        <v>4669</v>
       </c>
       <c r="P21" s="6">
-        <v>14544</v>
+        <v>14551</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0179171332586787</v>
+        <v>1.0184070548712205</v>
       </c>
       <c r="R21" s="7">
         <v>10910</v>
@@ -3862,14 +3862,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3702</v>
+        <v>3708</v>
       </c>
       <c r="U21" s="13">
-        <v>11200</v>
+        <v>11206</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0265811182401468</v>
+        <v>1.0271310724106324</v>
       </c>
       <c r="W21" s="7">
         <v>11256</v>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3686</v>
+        <v>3693</v>
       </c>
       <c r="Z21" s="13">
-        <v>11325</v>
+        <v>11332</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0061300639658848</v>
+        <v>1.0067519545131485</v>
       </c>
       <c r="AB21" s="7">
         <v>14831</v>
@@ -3896,14 +3896,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4909</v>
+        <v>4918</v>
       </c>
       <c r="AE21" s="6">
-        <v>14998</v>
+        <v>15007</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0112601982334299</v>
+        <v>1.011867035263974</v>
       </c>
       <c r="AG21" s="7">
         <v>11222</v>
@@ -3913,14 +3913,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3725</v>
+        <v>3734</v>
       </c>
       <c r="AJ21" s="6">
-        <v>11368</v>
+        <v>11377</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0130101586170024</v>
+        <v>1.0138121546961325</v>
       </c>
       <c r="AL21" s="7">
         <v>11337</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3505</v>
+        <v>3515</v>
       </c>
       <c r="AO21" s="6">
-        <v>11530</v>
+        <v>11540</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0170239040310487</v>
+        <v>1.0179059715974244</v>
       </c>
       <c r="AQ21" s="7">
         <v>15149</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4594</v>
+        <v>4608</v>
       </c>
       <c r="AT21" s="6">
-        <v>15408</v>
+        <v>15422</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0170968380751204</v>
+        <v>1.0180209914845864</v>
       </c>
       <c r="AV21" s="7">
         <v>11422</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3644</v>
+        <v>3653</v>
       </c>
       <c r="AY21" s="6">
-        <v>11718</v>
+        <v>11727</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0259149010681141</v>
+        <v>1.0267028541411312</v>
       </c>
       <c r="BA21" s="7">
         <v>11689</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3524</v>
+        <v>3534</v>
       </c>
       <c r="BD21" s="6">
-        <v>11846</v>
+        <v>11856</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0134314312601591</v>
+        <v>1.0142869364359655</v>
       </c>
       <c r="BF21" s="7">
         <v>15725</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6376</v>
+        <v>6395</v>
       </c>
       <c r="BI21" s="6">
-        <v>15821</v>
+        <v>15840</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0061049284578696</v>
+        <v>1.0073131955484897</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="F22" s="13">
-        <v>6685</v>
+        <v>6690</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.98949082297217283</v>
+        <v>0.99023090586145646</v>
       </c>
       <c r="H22" s="7">
         <v>6770</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1678</v>
+        <v>1683</v>
       </c>
       <c r="K22" s="13">
-        <v>6770</v>
+        <v>6775</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.000738552437223</v>
       </c>
       <c r="M22" s="7">
         <v>8074</v>
@@ -4057,14 +4057,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="P22" s="6">
-        <v>8087</v>
+        <v>8093</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0016101065147387</v>
+        <v>1.0023532325984643</v>
       </c>
       <c r="R22" s="7">
         <v>6748</v>
@@ -4074,14 +4074,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1761</v>
+        <v>1766</v>
       </c>
       <c r="U22" s="13">
-        <v>6796</v>
+        <v>6801</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.007113218731476</v>
+        <v>1.0078541790160047</v>
       </c>
       <c r="W22" s="7">
         <v>6876</v>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="Z22" s="13">
-        <v>6857</v>
+        <v>6862</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99723676556137286</v>
+        <v>0.99796393251890636</v>
       </c>
       <c r="AB22" s="7">
         <v>8219</v>
@@ -4108,14 +4108,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2257</v>
+        <v>2263</v>
       </c>
       <c r="AE22" s="6">
-        <v>8242</v>
+        <v>8248</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0027983939652025</v>
+        <v>1.0035284097822119</v>
       </c>
       <c r="AG22" s="7">
         <v>6901</v>
@@ -4125,14 +4125,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1733</v>
+        <v>1738</v>
       </c>
       <c r="AJ22" s="6">
-        <v>6915</v>
+        <v>6920</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.0020286914939864</v>
+        <v>1.00275322417041</v>
       </c>
       <c r="AL22" s="7">
         <v>6948</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="AO22" s="6">
-        <v>6950</v>
+        <v>6957</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>1.0002878526194587</v>
+        <v>1.0012953367875648</v>
       </c>
       <c r="AQ22" s="7">
         <v>8297</v>
@@ -4159,14 +4159,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2137</v>
+        <v>2144</v>
       </c>
       <c r="AT22" s="6">
-        <v>8312</v>
+        <v>8319</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0018078823671206</v>
+        <v>1.0026515608051103</v>
       </c>
       <c r="AV22" s="7">
         <v>6958</v>
@@ -4176,14 +4176,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1870</v>
+        <v>1876</v>
       </c>
       <c r="AY22" s="6">
-        <v>6996</v>
+        <v>7002</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>1.0054613394653635</v>
+        <v>1.0063236562230526</v>
       </c>
       <c r="BA22" s="7">
         <v>7049</v>
@@ -4193,14 +4193,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1752</v>
+        <v>1759</v>
       </c>
       <c r="BD22" s="6">
-        <v>7058</v>
+        <v>7065</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.0012767768477799</v>
+        <v>1.002269825507164</v>
       </c>
       <c r="BF22" s="7">
         <v>8436</v>
@@ -4210,14 +4210,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2685</v>
+        <v>2696</v>
       </c>
       <c r="BI22" s="6">
-        <v>8424</v>
+        <v>8435</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.99857752489331442</v>
+        <v>0.99988146040777615</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="F23" s="13">
-        <v>8682</v>
+        <v>8684</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.98569482288828336</v>
+        <v>0.98592188919164392</v>
       </c>
       <c r="H23" s="7">
         <v>8878</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="K23" s="13">
-        <v>8795</v>
+        <v>8798</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.99065104753322819</v>
+        <v>0.99098896147781035</v>
       </c>
       <c r="M23" s="7">
         <v>11255</v>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3415</v>
+        <v>3418</v>
       </c>
       <c r="P23" s="6">
-        <v>11221</v>
+        <v>11224</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.99697912039093739</v>
+        <v>0.99724566859173702</v>
       </c>
       <c r="R23" s="7">
         <v>8944</v>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="U23" s="13">
-        <v>8924</v>
+        <v>8927</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.99776386404293382</v>
+        <v>0.99809928443649376</v>
       </c>
       <c r="W23" s="7">
         <v>10422</v>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>2958</v>
+        <v>2961</v>
       </c>
       <c r="Z23" s="13">
-        <v>9035</v>
+        <v>9038</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.86691613893686437</v>
+        <v>0.86720399155632322</v>
       </c>
       <c r="AB23" s="7">
         <v>11673</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3734</v>
+        <v>3741</v>
       </c>
       <c r="AE23" s="6">
-        <v>11406</v>
+        <v>11413</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97712670264713442</v>
+        <v>0.97772637710956911</v>
       </c>
       <c r="AG23" s="7">
         <v>9370</v>
@@ -4337,14 +4337,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>4419</v>
+        <v>4426</v>
       </c>
       <c r="AJ23" s="6">
-        <v>9005</v>
+        <v>9012</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.96104589114194239</v>
+        <v>0.96179295624332972</v>
       </c>
       <c r="AL23" s="7">
         <v>9238</v>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2639</v>
+        <v>2646</v>
       </c>
       <c r="AO23" s="6">
-        <v>9042</v>
+        <v>9049</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.97878328642563328</v>
+        <v>0.97954102619614636</v>
       </c>
       <c r="AQ23" s="7">
         <v>11727</v>
@@ -4371,14 +4371,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3123</v>
+        <v>3135</v>
       </c>
       <c r="AT23" s="6">
-        <v>11535</v>
+        <v>11547</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.98362752622154004</v>
+        <v>0.98465080583269382</v>
       </c>
       <c r="AV23" s="7">
         <v>9359</v>
@@ -4388,14 +4388,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2782</v>
+        <v>2790</v>
       </c>
       <c r="AY23" s="6">
-        <v>9165</v>
+        <v>9173</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.9792712896676995</v>
+        <v>0.98012608184635108</v>
       </c>
       <c r="BA23" s="7">
         <v>9570</v>
@@ -4405,14 +4405,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2913</v>
+        <v>2922</v>
       </c>
       <c r="BD23" s="6">
-        <v>9222</v>
+        <v>9231</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.96363636363636362</v>
+        <v>0.96457680250783695</v>
       </c>
       <c r="BF23" s="7">
         <v>11968</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4327</v>
+        <v>4340</v>
       </c>
       <c r="BI23" s="6">
-        <v>11727</v>
+        <v>11740</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9798629679144385</v>
+        <v>0.98094919786096257</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="F24" s="13">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.98943999999999999</v>
+        <v>0.98960000000000004</v>
       </c>
       <c r="H24" s="7">
         <v>6322</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="K24" s="13">
-        <v>6235</v>
+        <v>6236</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.98623853211009171</v>
+        <v>0.98639670990192974</v>
       </c>
       <c r="M24" s="7">
         <v>7266</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="P24" s="6">
-        <v>7154</v>
+        <v>7156</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.98458574181117531</v>
+        <v>0.98486099642169012</v>
       </c>
       <c r="R24" s="7">
         <v>6403</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="U24" s="13">
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.983913790410745</v>
+        <v>0.98406996720287365</v>
       </c>
       <c r="W24" s="7">
         <v>6540</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="AE24" s="6">
-        <v>7377</v>
+        <v>7378</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98715375351264556</v>
+        <v>0.98728756858022215</v>
       </c>
       <c r="AG24" s="7">
         <v>6660</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="AJ24" s="6">
-        <v>6589</v>
+        <v>6590</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.98933933933933937</v>
+        <v>0.98948948948948945</v>
       </c>
       <c r="AL24" s="7">
         <v>6723</v>
@@ -4634,14 +4634,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="BI24" s="6">
-        <v>7748</v>
+        <v>7749</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.98349834983498352</v>
+        <v>0.98362528560548368</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4290</v>
+        <v>4294</v>
       </c>
       <c r="F25" s="13">
-        <v>20234</v>
+        <v>20238</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.96683868501529047</v>
+        <v>0.96702981651376152</v>
       </c>
       <c r="H25" s="7">
         <v>20519</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3848</v>
+        <v>3852</v>
       </c>
       <c r="K25" s="13">
-        <v>20335</v>
+        <v>20339</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.99103270139870359</v>
+        <v>0.99122764267264485</v>
       </c>
       <c r="M25" s="7">
         <v>27924</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>5560</v>
+        <v>5563</v>
       </c>
       <c r="P25" s="6">
-        <v>27892</v>
+        <v>27895</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.9988540323735855</v>
+        <v>0.9989614668385618</v>
       </c>
       <c r="R25" s="7">
         <v>20481</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4506</v>
+        <v>4509</v>
       </c>
       <c r="U25" s="13">
-        <v>20527</v>
+        <v>20530</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0022459840828084</v>
+        <v>1.0023924613056003</v>
       </c>
       <c r="W25" s="7">
         <v>20934</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4232</v>
+        <v>4236</v>
       </c>
       <c r="Z25" s="13">
-        <v>20631</v>
+        <v>20635</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.98552593866437377</v>
+        <v>0.98571701538167578</v>
       </c>
       <c r="AB25" s="7">
         <v>28211</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>6240</v>
+        <v>6250</v>
       </c>
       <c r="AE25" s="6">
-        <v>28199</v>
+        <v>28209</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.99957463400801105</v>
+        <v>0.99992910566800186</v>
       </c>
       <c r="AG25" s="7">
         <v>20778</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4165</v>
+        <v>4172</v>
       </c>
       <c r="AJ25" s="6">
-        <v>20730</v>
+        <v>20737</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.99768986427952644</v>
+        <v>0.99802675907209548</v>
       </c>
       <c r="AL25" s="7">
         <v>21081</v>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4110</v>
+        <v>4118</v>
       </c>
       <c r="AO25" s="6">
-        <v>20905</v>
+        <v>20913</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99165124994070486</v>
+        <v>0.99203073857976376</v>
       </c>
       <c r="AQ25" s="7">
         <v>28478</v>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5139</v>
+        <v>5151</v>
       </c>
       <c r="AT25" s="6">
-        <v>28464</v>
+        <v>28476</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.99950839244328959</v>
+        <v>0.9999297703490414</v>
       </c>
       <c r="AV25" s="7">
         <v>21086</v>
@@ -4812,14 +4812,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4339</v>
+        <v>4347</v>
       </c>
       <c r="AY25" s="6">
-        <v>21071</v>
+        <v>21079</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.99928862752537229</v>
+        <v>0.99966802617850703</v>
       </c>
       <c r="BA25" s="7">
         <v>21405</v>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4409</v>
+        <v>4418</v>
       </c>
       <c r="BD25" s="6">
-        <v>21241</v>
+        <v>21250</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.99233823872926885</v>
+        <v>0.99275870123802845</v>
       </c>
       <c r="BF25" s="7">
         <v>28924</v>
@@ -4846,14 +4846,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>8014</v>
+        <v>8030</v>
       </c>
       <c r="BI25" s="6">
-        <v>28828</v>
+        <v>28844</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.99668095699073433</v>
+        <v>0.99723413082561196</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3368</v>
+        <v>3377</v>
       </c>
       <c r="F26" s="13">
-        <v>14084</v>
+        <v>14093</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>1.0001420252805</v>
+        <v>1.0007811390427497</v>
       </c>
       <c r="H26" s="7">
         <v>14494</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3083</v>
+        <v>3090</v>
       </c>
       <c r="K26" s="13">
-        <v>14350</v>
+        <v>14357</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.99006485442251968</v>
+        <v>0.99054781288809157</v>
       </c>
       <c r="M26" s="7">
         <v>27473</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5295</v>
+        <v>5310</v>
       </c>
       <c r="P26" s="6">
-        <v>27410</v>
+        <v>27425</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.9977068394423616</v>
+        <v>0.99825283005132315</v>
       </c>
       <c r="R26" s="7">
         <v>14274</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3401</v>
+        <v>3409</v>
       </c>
       <c r="U26" s="13">
-        <v>14303</v>
+        <v>14311</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0020316659660922</v>
+        <v>1.0025921255429453</v>
       </c>
       <c r="W26" s="7">
         <v>14651</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3138</v>
+        <v>3146</v>
       </c>
       <c r="Z26" s="13">
-        <v>14451</v>
+        <v>14459</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.98634905467203604</v>
+        <v>0.98689509248515461</v>
       </c>
       <c r="AB26" s="7">
         <v>28023</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5784</v>
+        <v>5800</v>
       </c>
       <c r="AE26" s="6">
-        <v>27673</v>
+        <v>27689</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98751025942975412</v>
+        <v>0.98808121899867962</v>
       </c>
       <c r="AG26" s="7">
         <v>14346</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3088</v>
+        <v>3097</v>
       </c>
       <c r="AJ26" s="6">
-        <v>14319</v>
+        <v>14328</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.99811794228356332</v>
+        <v>0.99874529485570895</v>
       </c>
       <c r="AL26" s="7">
         <v>14687</v>
@@ -4990,14 +4990,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3007</v>
+        <v>3016</v>
       </c>
       <c r="AO26" s="6">
-        <v>14450</v>
+        <v>14459</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98386328045210047</v>
+        <v>0.98447606727037518</v>
       </c>
       <c r="AQ26" s="7">
         <v>27948</v>
@@ -5007,14 +5007,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5336</v>
+        <v>5355</v>
       </c>
       <c r="AT26" s="6">
-        <v>27809</v>
+        <v>27828</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99502647774438246</v>
+        <v>0.99570631172176904</v>
       </c>
       <c r="AV26" s="7">
         <v>14478</v>
@@ -5024,14 +5024,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3188</v>
+        <v>3198</v>
       </c>
       <c r="AY26" s="6">
-        <v>14445</v>
+        <v>14455</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.9977206796518856</v>
+        <v>0.99841138278767783</v>
       </c>
       <c r="BA26" s="7">
         <v>14902</v>
@@ -5041,14 +5041,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3095</v>
+        <v>3105</v>
       </c>
       <c r="BD26" s="6">
-        <v>14561</v>
+        <v>14571</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97711716548114347</v>
+        <v>0.97778821634679913</v>
       </c>
       <c r="BF26" s="7">
         <v>28105</v>
@@ -5058,14 +5058,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6588</v>
+        <v>6609</v>
       </c>
       <c r="BI26" s="6">
-        <v>27927</v>
+        <v>27948</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99366660736523749</v>
+        <v>0.99441380537270951</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>36771</v>
+        <v>36794</v>
       </c>
       <c r="F27" s="13">
-        <v>125305</v>
+        <v>125328</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.97032608779822982</v>
+        <v>0.97050419322115278</v>
       </c>
       <c r="H27" s="7">
         <v>129298</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32491</v>
+        <v>32518</v>
       </c>
       <c r="K27" s="13">
-        <v>126156</v>
+        <v>126183</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.97569954678339954</v>
+        <v>0.9759083667187427</v>
       </c>
       <c r="M27" s="7">
         <v>186733</v>
@@ -5117,14 +5117,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47851</v>
+        <v>47900</v>
       </c>
       <c r="P27" s="6">
-        <v>185399</v>
+        <v>185448</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99285611006088903</v>
+        <v>0.99311851681277541</v>
       </c>
       <c r="R27" s="7">
         <v>126872</v>
@@ -5134,14 +5134,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32607</v>
+        <v>32643</v>
       </c>
       <c r="U27" s="13">
-        <v>125830</v>
+        <v>125866</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99178699791916258</v>
+        <v>0.99207074847089982</v>
       </c>
       <c r="W27" s="7">
         <v>129739</v>
@@ -5151,14 +5151,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>33860</v>
+        <v>33899</v>
       </c>
       <c r="Z27" s="13">
-        <v>126721</v>
+        <v>126760</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97673791227001905</v>
+        <v>0.9770385157893926</v>
       </c>
       <c r="AB27" s="7">
         <v>188270</v>
@@ -5168,14 +5168,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>52558</v>
+        <v>52623</v>
       </c>
       <c r="AE27" s="6">
-        <v>186889</v>
+        <v>186954</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99266478992935681</v>
+        <v>0.99301003877410099</v>
       </c>
       <c r="AG27" s="7">
         <v>127800</v>
@@ -5185,14 +5185,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34265</v>
+        <v>34304</v>
       </c>
       <c r="AJ27" s="6">
-        <v>126951</v>
+        <v>126990</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99335680751173705</v>
+        <v>0.99366197183098592</v>
       </c>
       <c r="AL27" s="7">
         <v>130262</v>
@@ -5202,14 +5202,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31040</v>
+        <v>31082</v>
       </c>
       <c r="AO27" s="6">
-        <v>127874</v>
+        <v>127916</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98166771583424173</v>
+        <v>0.98199014294268472</v>
       </c>
       <c r="AQ27" s="7">
         <v>189830</v>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>45157</v>
+        <v>45231</v>
       </c>
       <c r="AT27" s="6">
-        <v>188971</v>
+        <v>189045</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99547489859347837</v>
+        <v>0.99586472106621715</v>
       </c>
       <c r="AV27" s="7">
         <v>128733</v>
@@ -5236,14 +5236,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30954</v>
+        <v>30997</v>
       </c>
       <c r="AY27" s="6">
-        <v>128695</v>
+        <v>128738</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99970481539310041</v>
+        <v>1.0000388400798552</v>
       </c>
       <c r="BA27" s="7">
         <v>132099</v>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31446</v>
+        <v>31495</v>
       </c>
       <c r="BD27" s="6">
-        <v>130122</v>
+        <v>130171</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98503395180887066</v>
+        <v>0.98540488572964213</v>
       </c>
       <c r="BF27" s="7">
         <v>192460</v>
@@ -5270,14 +5270,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65145</v>
+        <v>65247</v>
       </c>
       <c r="BI27" s="6">
-        <v>191551</v>
+        <v>191653</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99527694066299488</v>
+        <v>0.99580692091863243</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>69893</v>
+        <v>69917</v>
       </c>
       <c r="F28" s="13">
-        <v>409738</v>
+        <v>409762</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99128082798263906</v>
+        <v>0.99133889128131181</v>
       </c>
       <c r="H28" s="7">
         <v>423216</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63942</v>
+        <v>63961</v>
       </c>
       <c r="K28" s="13">
-        <v>413995</v>
+        <v>414014</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.97821207137726363</v>
+        <v>0.97825696571018106</v>
       </c>
       <c r="M28" s="7">
         <v>688530</v>
@@ -5329,14 +5329,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>102848</v>
+        <v>102882</v>
       </c>
       <c r="P28" s="6">
-        <v>681011</v>
+        <v>681045</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.98907963342192784</v>
+        <v>0.98912901398631869</v>
       </c>
       <c r="R28" s="7">
         <v>417505</v>
@@ -5346,14 +5346,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>65537</v>
+        <v>65556</v>
       </c>
       <c r="U28" s="13">
-        <v>414366</v>
+        <v>414385</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99248152716733928</v>
+        <v>0.99252703560436406</v>
       </c>
       <c r="W28" s="7">
         <v>426115</v>
@@ -5363,14 +5363,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67669</v>
+        <v>67693</v>
       </c>
       <c r="Z28" s="13">
-        <v>416334</v>
+        <v>416358</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.97704610257794255</v>
+        <v>0.97710242540159342</v>
       </c>
       <c r="AB28" s="7">
         <v>693825</v>
@@ -5380,14 +5380,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>118219</v>
+        <v>118271</v>
       </c>
       <c r="AE28" s="6">
-        <v>686284</v>
+        <v>686336</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98913126508845894</v>
+        <v>0.98920621194105141</v>
       </c>
       <c r="AG28" s="7">
         <v>421441</v>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>73217</v>
+        <v>73245</v>
       </c>
       <c r="AJ28" s="6">
-        <v>417057</v>
+        <v>417085</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98959759491838717</v>
+        <v>0.98966403363697408</v>
       </c>
       <c r="AL28" s="7">
         <v>428935</v>
@@ -5414,14 +5414,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>62077</v>
+        <v>62110</v>
       </c>
       <c r="AO28" s="6">
-        <v>421308</v>
+        <v>421341</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98221875109282297</v>
+        <v>0.98229568582652382</v>
       </c>
       <c r="AQ28" s="7">
         <v>700018</v>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>95313</v>
+        <v>95406</v>
       </c>
       <c r="AT28" s="6">
-        <v>695249</v>
+        <v>695342</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99318731804039329</v>
+        <v>0.99332017176701171</v>
       </c>
       <c r="AV28" s="7">
         <v>428584</v>
@@ -5448,14 +5448,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>63359</v>
+        <v>63405</v>
       </c>
       <c r="AY28" s="6">
-        <v>426776</v>
+        <v>426822</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99578145707725907</v>
+        <v>0.99588878726224028</v>
       </c>
       <c r="BA28" s="7">
         <v>438333</v>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>63318</v>
+        <v>63377</v>
       </c>
       <c r="BD28" s="6">
-        <v>431769</v>
+        <v>431828</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98502508366926511</v>
+        <v>0.98515968453207947</v>
       </c>
       <c r="BF28" s="7">
         <v>711748</v>
@@ -5482,14 +5482,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>139216</v>
+        <v>139352</v>
       </c>
       <c r="BI28" s="6">
-        <v>706225</v>
+        <v>706361</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99224023109302728</v>
+        <v>0.99243130995801887</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5507,14 +5507,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>26029</v>
+        <v>26033</v>
       </c>
       <c r="F29" s="13">
-        <v>135542</v>
+        <v>135546</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99084755179320727</v>
+        <v>0.99087679284179131</v>
       </c>
       <c r="H29" s="7">
         <v>138439</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>24303</v>
+        <v>24308</v>
       </c>
       <c r="K29" s="13">
-        <v>136682</v>
+        <v>136687</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98730848965970575</v>
+        <v>0.98734460664986023</v>
       </c>
       <c r="M29" s="7">
         <v>184711</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>32705</v>
+        <v>32720</v>
       </c>
       <c r="P29" s="6">
-        <v>182807</v>
+        <v>182822</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98969200534889634</v>
+        <v>0.98977321328995027</v>
       </c>
       <c r="R29" s="7">
         <v>138323</v>
@@ -5558,14 +5558,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26927</v>
+        <v>26934</v>
       </c>
       <c r="U29" s="13">
-        <v>136889</v>
+        <v>136896</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98963296053440142</v>
+        <v>0.98968356672426128</v>
       </c>
       <c r="W29" s="7">
         <v>139858</v>
@@ -5575,14 +5575,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>25752</v>
+        <v>25761</v>
       </c>
       <c r="Z29" s="13">
-        <v>137304</v>
+        <v>137313</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98173862060089523</v>
+        <v>0.98180297158546526</v>
       </c>
       <c r="AB29" s="7">
         <v>187429</v>
@@ -5592,14 +5592,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>36091</v>
+        <v>36108</v>
       </c>
       <c r="AE29" s="6">
-        <v>184191</v>
+        <v>184208</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98272412486861693</v>
+        <v>0.98281482588073354</v>
       </c>
       <c r="AG29" s="7">
         <v>139419</v>
@@ -5609,14 +5609,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>38034</v>
+        <v>38044</v>
       </c>
       <c r="AJ29" s="6">
-        <v>138029</v>
+        <v>138039</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.99003005329259286</v>
+        <v>0.99010177952789791</v>
       </c>
       <c r="AL29" s="7">
         <v>141276</v>
@@ -5626,14 +5626,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23679</v>
+        <v>23691</v>
       </c>
       <c r="AO29" s="6">
-        <v>139185</v>
+        <v>139197</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98519918457487476</v>
+        <v>0.98528412469209203</v>
       </c>
       <c r="AQ29" s="7">
         <v>188424</v>
@@ -5643,14 +5643,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29834</v>
+        <v>29866</v>
       </c>
       <c r="AT29" s="6">
-        <v>186843</v>
+        <v>186875</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99160934912749965</v>
+        <v>0.99177917887317968</v>
       </c>
       <c r="AV29" s="7">
         <v>141887</v>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>24998</v>
+        <v>25014</v>
       </c>
       <c r="AY29" s="6">
-        <v>140587</v>
+        <v>140603</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99083777935963124</v>
+        <v>0.9909505451521281</v>
       </c>
       <c r="BA29" s="7">
         <v>143795</v>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>25538</v>
+        <v>25556</v>
       </c>
       <c r="BD29" s="6">
-        <v>141674</v>
+        <v>141692</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98524983483431272</v>
+        <v>0.98537501303939634</v>
       </c>
       <c r="BF29" s="7">
         <v>191754</v>
@@ -5694,14 +5694,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>43956</v>
+        <v>43999</v>
       </c>
       <c r="BI29" s="6">
-        <v>189266</v>
+        <v>189309</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.98702504250237288</v>
+        <v>0.98724928815044277</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41597</v>
+        <v>41608</v>
       </c>
       <c r="F30" s="13">
-        <v>176270</v>
+        <v>176281</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.98891419723303753</v>
+        <v>0.98897590969783333</v>
       </c>
       <c r="H30" s="7">
         <v>181910</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39145</v>
+        <v>39156</v>
       </c>
       <c r="K30" s="13">
-        <v>178414</v>
+        <v>178425</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98078170523885433</v>
+        <v>0.98084217470177559</v>
       </c>
       <c r="M30" s="7">
         <v>304709</v>
@@ -5753,14 +5753,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>61695</v>
+        <v>61714</v>
       </c>
       <c r="P30" s="6">
-        <v>300966</v>
+        <v>300985</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98771614885021441</v>
+        <v>0.98777850342457885</v>
       </c>
       <c r="R30" s="7">
         <v>179361</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37709</v>
+        <v>37720</v>
       </c>
       <c r="U30" s="13">
-        <v>178096</v>
+        <v>178107</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99294718472800669</v>
+        <v>0.99300851355645881</v>
       </c>
       <c r="W30" s="7">
         <v>184404</v>
@@ -5787,14 +5787,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38741</v>
+        <v>38756</v>
       </c>
       <c r="Z30" s="13">
-        <v>179274</v>
+        <v>179289</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.97218064684063255</v>
+        <v>0.97226198997852542</v>
       </c>
       <c r="AB30" s="7">
         <v>307610</v>
@@ -5804,14 +5804,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>66720</v>
+        <v>66750</v>
       </c>
       <c r="AE30" s="6">
-        <v>303916</v>
+        <v>303946</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98799128766945155</v>
+        <v>0.98808881375768021</v>
       </c>
       <c r="AG30" s="7">
         <v>180656</v>
@@ -5821,14 +5821,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38765</v>
+        <v>38782</v>
       </c>
       <c r="AJ30" s="6">
-        <v>179091</v>
+        <v>179108</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99133712691524223</v>
+        <v>0.99143122841200959</v>
       </c>
       <c r="AL30" s="7">
         <v>185185</v>
@@ -5838,14 +5838,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34634</v>
+        <v>34654</v>
       </c>
       <c r="AO30" s="6">
-        <v>181855</v>
+        <v>181875</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98201798201798207</v>
+        <v>0.98212598212598212</v>
       </c>
       <c r="AQ30" s="7">
         <v>311830</v>
@@ -5855,14 +5855,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>56032</v>
+        <v>56072</v>
       </c>
       <c r="AT30" s="6">
-        <v>308967</v>
+        <v>309007</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99081871532565824</v>
+        <v>0.9909469903473046</v>
       </c>
       <c r="AV30" s="7">
         <v>184055</v>
@@ -5872,14 +5872,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36895</v>
+        <v>36917</v>
       </c>
       <c r="AY30" s="6">
-        <v>182838</v>
+        <v>182860</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.9933878460242862</v>
+        <v>0.99350737551275436</v>
       </c>
       <c r="BA30" s="7">
         <v>188792</v>
@@ -5889,14 +5889,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>37264</v>
+        <v>37292</v>
       </c>
       <c r="BD30" s="6">
-        <v>185144</v>
+        <v>185172</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.9806771473367516</v>
+        <v>0.98082545870587734</v>
       </c>
       <c r="BF30" s="7">
         <v>315967</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>79688</v>
+        <v>79738</v>
       </c>
       <c r="BI30" s="6">
-        <v>313395</v>
+        <v>313445</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.9918599094209205</v>
+        <v>0.99201815379454183</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21592</v>
+        <v>21595</v>
       </c>
       <c r="F31" s="13">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0039661857242739</v>
+        <v>1.0040043221254689</v>
       </c>
       <c r="H31" s="7">
         <v>80911</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18859</v>
+        <v>18864</v>
       </c>
       <c r="K31" s="13">
-        <v>80551</v>
+        <v>80556</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99555066678201976</v>
+        <v>0.99561246307671392</v>
       </c>
       <c r="M31" s="7">
         <v>142260</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>37923</v>
+        <v>37929</v>
       </c>
       <c r="P31" s="6">
-        <v>142460</v>
+        <v>142466</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0014058765640377</v>
+        <v>1.0014480528609588</v>
       </c>
       <c r="R31" s="7">
         <v>79665</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20845</v>
+        <v>20850</v>
       </c>
       <c r="U31" s="13">
-        <v>80191</v>
+        <v>80196</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0066026485909747</v>
+        <v>1.0066654114102807</v>
       </c>
       <c r="W31" s="7">
         <v>81657</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>20890</v>
+        <v>20895</v>
       </c>
       <c r="Z31" s="13">
-        <v>80907</v>
+        <v>80912</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99081523935486238</v>
+        <v>0.99087647109249666</v>
       </c>
       <c r="AB31" s="7">
         <v>144167</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>39696</v>
+        <v>39711</v>
       </c>
       <c r="AE31" s="6">
-        <v>144333</v>
+        <v>144348</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0011514424244106</v>
+        <v>1.0012554884266163</v>
       </c>
       <c r="AG31" s="7">
         <v>80917</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>21032</v>
+        <v>21040</v>
       </c>
       <c r="AJ31" s="6">
-        <v>81712</v>
+        <v>81720</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0098248822867877</v>
+        <v>1.0099237490267805</v>
       </c>
       <c r="AL31" s="7">
         <v>83546</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18187</v>
+        <v>18194</v>
       </c>
       <c r="AO31" s="6">
-        <v>82877</v>
+        <v>82884</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99199243530510139</v>
+        <v>0.99207622148277597</v>
       </c>
       <c r="AQ31" s="7">
         <v>147023</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>33084</v>
+        <v>33102</v>
       </c>
       <c r="AT31" s="6">
-        <v>147039</v>
+        <v>147057</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0001088265101379</v>
+        <v>1.000231256334043</v>
       </c>
       <c r="AV31" s="7">
         <v>81694</v>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18633</v>
+        <v>18642</v>
       </c>
       <c r="AY31" s="6">
-        <v>82608</v>
+        <v>82617</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0111880921487502</v>
+        <v>1.0112982593580924</v>
       </c>
       <c r="BA31" s="7">
         <v>83957</v>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18477</v>
+        <v>18485</v>
       </c>
       <c r="BD31" s="6">
-        <v>83625</v>
+        <v>83633</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99604559476875065</v>
+        <v>0.99614088164179282</v>
       </c>
       <c r="BF31" s="7">
         <v>148810</v>
@@ -6118,14 +6118,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>50295</v>
+        <v>50318</v>
       </c>
       <c r="BI31" s="6">
-        <v>149085</v>
+        <v>149108</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0018479940864189</v>
+        <v>1.0020025535918284</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>47089</v>
+        <v>47091</v>
       </c>
       <c r="F32" s="13">
-        <v>218153</v>
+        <v>218155</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99344241392029797</v>
+        <v>0.99345152167874207</v>
       </c>
       <c r="H32" s="7">
         <v>225984</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42412</v>
+        <v>42419</v>
       </c>
       <c r="K32" s="13">
-        <v>222633</v>
+        <v>222640</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98517151656754465</v>
+        <v>0.98520249221183798</v>
       </c>
       <c r="M32" s="7">
         <v>469379</v>
@@ -6177,14 +6177,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>100165</v>
+        <v>100176</v>
       </c>
       <c r="P32" s="6">
-        <v>465892</v>
+        <v>465903</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99257103534670277</v>
+        <v>0.99259447056642924</v>
       </c>
       <c r="R32" s="7">
         <v>220673</v>
@@ -6194,14 +6194,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>47735</v>
+        <v>47742</v>
       </c>
       <c r="U32" s="13">
-        <v>219984</v>
+        <v>219991</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99687773311642114</v>
+        <v>0.99690945426037625</v>
       </c>
       <c r="W32" s="7">
         <v>228851</v>
@@ -6211,14 +6211,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>48097</v>
+        <v>48106</v>
       </c>
       <c r="Z32" s="13">
-        <v>223047</v>
+        <v>223056</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.97463852025990705</v>
+        <v>0.97467784715819461</v>
       </c>
       <c r="AB32" s="7">
         <v>476427</v>
@@ -6228,14 +6228,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>106629</v>
+        <v>106650</v>
       </c>
       <c r="AE32" s="6">
-        <v>471763</v>
+        <v>471784</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99021046246329447</v>
+        <v>0.99025454056969908</v>
       </c>
       <c r="AG32" s="7">
         <v>224544</v>
@@ -6245,14 +6245,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>46695</v>
+        <v>46707</v>
       </c>
       <c r="AJ32" s="6">
-        <v>223779</v>
+        <v>223791</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99659309533988882</v>
+        <v>0.99664653698161609</v>
       </c>
       <c r="AL32" s="7">
         <v>231787</v>
@@ -6262,14 +6262,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>39804</v>
+        <v>39816</v>
       </c>
       <c r="AO32" s="6">
-        <v>227530</v>
+        <v>227542</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.98163400018120084</v>
+        <v>0.98168577185088035</v>
       </c>
       <c r="AQ32" s="7">
         <v>484390</v>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>81096</v>
+        <v>81123</v>
       </c>
       <c r="AT32" s="6">
-        <v>480496</v>
+        <v>480523</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99196102314250911</v>
+        <v>0.99201676335184463</v>
       </c>
       <c r="AV32" s="7">
         <v>227629</v>
@@ -6296,14 +6296,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40951</v>
+        <v>40967</v>
       </c>
       <c r="AY32" s="6">
-        <v>227633</v>
+        <v>227649</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>1.0000175724534219</v>
+        <v>1.0000878622671101</v>
       </c>
       <c r="BA32" s="7">
         <v>234918</v>
@@ -6313,14 +6313,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>43834</v>
+        <v>43848</v>
       </c>
       <c r="BD32" s="6">
-        <v>232013</v>
+        <v>232027</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98763398292170035</v>
+        <v>0.98769357818472825</v>
       </c>
       <c r="BF32" s="7">
         <v>492680</v>
@@ -6330,14 +6330,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>132809</v>
+        <v>132852</v>
       </c>
       <c r="BI32" s="6">
-        <v>489745</v>
+        <v>489788</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99404278639279042</v>
+        <v>0.99413006413899485</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>75787</v>
+        <v>75792</v>
       </c>
       <c r="F33" s="13">
-        <v>664236</v>
+        <v>664241</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.001242063755253</v>
+        <v>1.0012496005498845</v>
       </c>
       <c r="H33" s="7">
         <v>674602</v>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>68709</v>
+        <v>68713</v>
       </c>
       <c r="K33" s="13">
-        <v>671932</v>
+        <v>671936</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>0.99604211075567517</v>
+        <v>0.99604804017776405</v>
       </c>
       <c r="M33" s="7">
         <v>1077651</v>
@@ -6389,14 +6389,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>129443</v>
+        <v>129450</v>
       </c>
       <c r="P33" s="6">
-        <v>1076832</v>
+        <v>1076839</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>0.99924001369645643</v>
+        <v>0.99924650930588843</v>
       </c>
       <c r="R33" s="7">
         <v>670885</v>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>79600</v>
+        <v>79605</v>
       </c>
       <c r="U33" s="13">
-        <v>672482</v>
+        <v>672487</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0023804377799475</v>
+        <v>1.0023878906220887</v>
       </c>
       <c r="W33" s="7">
         <v>679851</v>
@@ -6423,14 +6423,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>75702</v>
+        <v>75709</v>
       </c>
       <c r="Z33" s="13">
-        <v>678487</v>
+        <v>678494</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>0.99799367802650873</v>
+        <v>0.998003974400273</v>
       </c>
       <c r="AB33" s="7">
         <v>1091619</v>
@@ -6440,14 +6440,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>137592</v>
+        <v>137600</v>
       </c>
       <c r="AE33" s="6">
-        <v>1090586</v>
+        <v>1090594</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99905369913861886</v>
+        <v>0.99906102770288896</v>
       </c>
       <c r="AG33" s="7">
         <v>681949</v>
@@ -6457,14 +6457,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>85554</v>
+        <v>85562</v>
       </c>
       <c r="AJ33" s="6">
-        <v>683865</v>
+        <v>683873</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.0028095942658468</v>
+        <v>1.0028213253483764</v>
       </c>
       <c r="AL33" s="7">
         <v>691548</v>
@@ -6474,14 +6474,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>66493</v>
+        <v>66501</v>
       </c>
       <c r="AO33" s="6">
-        <v>689418</v>
+        <v>689426</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>0.99691995349563589</v>
+        <v>0.99693152174541755</v>
       </c>
       <c r="AQ33" s="7">
         <v>1107071</v>
@@ -6491,14 +6491,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>112177</v>
+        <v>112186</v>
       </c>
       <c r="AT33" s="6">
-        <v>1108820</v>
+        <v>1108829</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0015798444724864</v>
+        <v>1.0015879740323792</v>
       </c>
       <c r="AV33" s="7">
         <v>697202</v>
@@ -6508,14 +6508,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>69920</v>
+        <v>69927</v>
       </c>
       <c r="AY33" s="6">
-        <v>700268</v>
+        <v>700275</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.004397577746478</v>
+        <v>1.0044076178783194</v>
       </c>
       <c r="BA33" s="7">
         <v>707985</v>
@@ -6525,14 +6525,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>69602</v>
+        <v>69612</v>
       </c>
       <c r="BD33" s="6">
-        <v>709731</v>
+        <v>709741</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0024661539439395</v>
+        <v>1.0024802785369746</v>
       </c>
       <c r="BF33" s="7">
         <v>1132408</v>
@@ -6542,14 +6542,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>174787</v>
+        <v>174813</v>
       </c>
       <c r="BI33" s="6">
-        <v>1133237</v>
+        <v>1133263</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>1.0007320683004712</v>
+        <v>1.0007550282230433</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6806,14 +6806,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="U35" s="13">
-        <v>11976</v>
+        <v>11977</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99361154899195225</v>
+        <v>0.9936945158881606</v>
       </c>
       <c r="W35" s="7">
         <v>12107</v>
@@ -6857,14 +6857,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" si="12"/>
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="AJ35" s="6">
-        <v>12039</v>
+        <v>12040</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK47" si="36">AJ35/AG35</f>
-        <v>0.99693607154686981</v>
+        <v>0.99701888042398146</v>
       </c>
       <c r="AL35" s="7">
         <v>12179</v>
@@ -6874,14 +6874,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="37">AO35-AM35</f>
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="AO35" s="6">
-        <v>12095</v>
+        <v>12096</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="38">AO35/AL35</f>
-        <v>0.99310288201001728</v>
+        <v>0.99318499055751708</v>
       </c>
       <c r="AQ35" s="7">
         <v>14849</v>
@@ -6891,14 +6891,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="39">AT35-AR35</f>
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="AT35" s="6">
-        <v>14840</v>
+        <v>14841</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="40">AT35/AQ35</f>
-        <v>0.99939389857902894</v>
+        <v>0.99946124318135898</v>
       </c>
       <c r="AV35" s="7">
         <v>12178</v>
@@ -6908,14 +6908,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="41">AY35-AW35</f>
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="AY35" s="6">
-        <v>12198</v>
+        <v>12199</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="42">AY35/AV35</f>
-        <v>1.0016423057973394</v>
+        <v>1.0017244210872065</v>
       </c>
       <c r="BA35" s="7">
         <v>12308</v>
@@ -6925,14 +6925,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="43">BD35-BB35</f>
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="BD35" s="6">
-        <v>12250</v>
+        <v>12251</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="44">BD35/BA35</f>
-        <v>0.99528761780955477</v>
+        <v>0.99536886577835559</v>
       </c>
       <c r="BF35" s="7">
         <v>15013</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>3324</v>
+        <v>3326</v>
       </c>
       <c r="BI35" s="6">
-        <v>14964</v>
+        <v>14966</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99673616199293946</v>
+        <v>0.99686937987077862</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>186813</v>
+        <v>186830</v>
       </c>
       <c r="F36" s="13">
-        <v>888497</v>
+        <v>888514</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>0.99287829517136572</v>
+        <v>0.99289729234413937</v>
       </c>
       <c r="H36" s="7">
         <v>910737</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>161978</v>
+        <v>162001</v>
       </c>
       <c r="K36" s="13">
-        <v>898775</v>
+        <v>898798</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.98686558248978573</v>
+        <v>0.98689083676187528</v>
       </c>
       <c r="M36" s="7">
         <v>1579599</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>319619</v>
+        <v>319662</v>
       </c>
       <c r="P36" s="6">
-        <v>1568445</v>
+        <v>1568488</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.99293871419265267</v>
+        <v>0.99296593629142582</v>
       </c>
       <c r="R36" s="7">
         <v>901122</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>174504</v>
+        <v>174533</v>
       </c>
       <c r="U36" s="13">
-        <v>898800</v>
+        <v>898829</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>0.99742321239521392</v>
+        <v>0.99745539449708254</v>
       </c>
       <c r="W36" s="7">
         <v>923866</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>178550</v>
+        <v>178583</v>
       </c>
       <c r="Z36" s="13">
-        <v>907779</v>
+        <v>907812</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98258730162166374</v>
+        <v>0.98262302108747368</v>
       </c>
       <c r="AB36" s="7">
         <v>1592928</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>337312</v>
+        <v>337378</v>
       </c>
       <c r="AE36" s="6">
-        <v>1585601</v>
+        <v>1585667</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.99540029430080956</v>
+        <v>0.99544172743526382</v>
       </c>
       <c r="AG36" s="7">
         <v>914936</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>305786</v>
+        <v>305821</v>
       </c>
       <c r="AJ36" s="6">
-        <v>913012</v>
+        <v>913047</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99789712067292136</v>
+        <v>0.99793537471473415</v>
       </c>
       <c r="AL36" s="7">
         <v>934551</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162983</v>
+        <v>163031</v>
       </c>
       <c r="AO36" s="6">
-        <v>923127</v>
+        <v>923175</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98777594802209834</v>
+        <v>0.98782730958503062</v>
       </c>
       <c r="AQ36" s="7">
         <v>1610673</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>275092</v>
+        <v>275185</v>
       </c>
       <c r="AT36" s="6">
-        <v>1610312</v>
+        <v>1610405</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99977587008660351</v>
+        <v>0.99983360992578874</v>
       </c>
       <c r="AV36" s="7">
         <v>933166</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>163572</v>
+        <v>163627</v>
       </c>
       <c r="AY36" s="6">
-        <v>934898</v>
+        <v>934953</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>1.001856047048435</v>
+        <v>1.0019149861868093</v>
       </c>
       <c r="BA36" s="7">
         <v>952259</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>160740</v>
+        <v>160804</v>
       </c>
       <c r="BD36" s="6">
-        <v>945711</v>
+        <v>945775</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.99312371949228095</v>
+        <v>0.99319092809834297</v>
       </c>
       <c r="BF36" s="7">
         <v>1640364</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>394649</v>
+        <v>394821</v>
       </c>
       <c r="BI36" s="6">
-        <v>1638804</v>
+        <v>1638976</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.9990489915652867</v>
+        <v>0.99915384634142179</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>134766</v>
+        <v>134793</v>
       </c>
       <c r="F37" s="13">
-        <v>700903</v>
+        <v>700930</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.98747383043530945</v>
+        <v>0.98751186964105075</v>
       </c>
       <c r="H37" s="7">
         <v>717455</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>120999</v>
+        <v>121030</v>
       </c>
       <c r="K37" s="13">
-        <v>706594</v>
+        <v>706625</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98486176833390249</v>
+        <v>0.98490497661874266</v>
       </c>
       <c r="M37" s="7">
         <v>885615</v>
@@ -7213,14 +7213,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>157111</v>
+        <v>157155</v>
       </c>
       <c r="P37" s="6">
-        <v>877810</v>
+        <v>877854</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99118691530744174</v>
+        <v>0.99123659829609934</v>
       </c>
       <c r="R37" s="7">
         <v>713906</v>
@@ -7230,14 +7230,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>125377</v>
+        <v>125409</v>
       </c>
       <c r="U37" s="13">
-        <v>707685</v>
+        <v>707717</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99128596762038701</v>
+        <v>0.99133079144873415</v>
       </c>
       <c r="W37" s="7">
         <v>721933</v>
@@ -7247,14 +7247,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>128707</v>
+        <v>128746</v>
       </c>
       <c r="Z37" s="13">
-        <v>709330</v>
+        <v>709369</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98254270133100996</v>
+        <v>0.98259672296459644</v>
       </c>
       <c r="AB37" s="7">
         <v>896229</v>
@@ -7264,14 +7264,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>180475</v>
+        <v>180531</v>
       </c>
       <c r="AE37" s="6">
-        <v>883263</v>
+        <v>883319</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98553271541090504</v>
+        <v>0.98559519944121421</v>
       </c>
       <c r="AG37" s="7">
         <v>721282</v>
@@ -7281,14 +7281,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>136424</v>
+        <v>136471</v>
       </c>
       <c r="AJ37" s="6">
-        <v>711980</v>
+        <v>712027</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98710351845741329</v>
+        <v>0.98716868021106863</v>
       </c>
       <c r="AL37" s="7">
         <v>727480</v>
@@ -7298,14 +7298,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>121946</v>
+        <v>121998</v>
       </c>
       <c r="AO37" s="6">
-        <v>717693</v>
+        <v>717745</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98654670918788145</v>
+        <v>0.98661818881618735</v>
       </c>
       <c r="AQ37" s="7">
         <v>903787</v>
@@ -7315,14 +7315,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>145290</v>
+        <v>145367</v>
       </c>
       <c r="AT37" s="6">
-        <v>895709</v>
+        <v>895786</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99106205333778863</v>
+        <v>0.99114725040302643</v>
       </c>
       <c r="AV37" s="7">
         <v>732294</v>
@@ -7332,14 +7332,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>126068</v>
+        <v>126135</v>
       </c>
       <c r="AY37" s="6">
-        <v>726278</v>
+        <v>726345</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99178472034456111</v>
+        <v>0.99187621365189393</v>
       </c>
       <c r="BA37" s="7">
         <v>740889</v>
@@ -7349,14 +7349,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>122963</v>
+        <v>123038</v>
       </c>
       <c r="BD37" s="6">
-        <v>731122</v>
+        <v>731197</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98681718853971379</v>
+        <v>0.98691841827858151</v>
       </c>
       <c r="BF37" s="7">
         <v>918028</v>
@@ -7366,14 +7366,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>217388</v>
+        <v>217507</v>
       </c>
       <c r="BI37" s="6">
-        <v>908414</v>
+        <v>908533</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98952755253652391</v>
+        <v>0.98965717821242927</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="F38" s="13">
-        <v>24505</v>
+        <v>24506</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0061588996099364</v>
+        <v>1.0061999589406692</v>
       </c>
       <c r="H38" s="7">
         <v>24747</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>5631</v>
+        <v>5634</v>
       </c>
       <c r="K38" s="13">
-        <v>24728</v>
+        <v>24731</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99923223016931351</v>
+        <v>0.99935345698468503</v>
       </c>
       <c r="M38" s="7">
         <v>37604</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>8988</v>
+        <v>8992</v>
       </c>
       <c r="P38" s="6">
-        <v>37777</v>
+        <v>37781</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0046005744069779</v>
+        <v>1.004706946069567</v>
       </c>
       <c r="R38" s="7">
         <v>24596</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>5848</v>
+        <v>5851</v>
       </c>
       <c r="U38" s="13">
-        <v>24826</v>
+        <v>24829</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.0093511140022768</v>
+        <v>1.0094730850544804</v>
       </c>
       <c r="W38" s="7">
         <v>25148</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6056</v>
+        <v>6058</v>
       </c>
       <c r="Z38" s="13">
-        <v>25008</v>
+        <v>25010</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.99443295689518052</v>
+        <v>0.99451248608239229</v>
       </c>
       <c r="AB38" s="7">
         <v>38035</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>9602</v>
+        <v>9605</v>
       </c>
       <c r="AE38" s="6">
-        <v>38190</v>
+        <v>38193</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>1.0040751939003549</v>
+        <v>1.0041540686210069</v>
       </c>
       <c r="AG38" s="7">
         <v>24962</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="12"/>
-        <v>6308</v>
+        <v>6310</v>
       </c>
       <c r="AJ38" s="6">
-        <v>25221</v>
+        <v>25223</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0103757711721817</v>
+        <v>1.0104558929572951</v>
       </c>
       <c r="AL38" s="7">
         <v>25436</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5902</v>
+        <v>5905</v>
       </c>
       <c r="AO38" s="6">
-        <v>25482</v>
+        <v>25485</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>1.0018084604497564</v>
+        <v>1.0019264035225663</v>
       </c>
       <c r="AQ38" s="7">
         <v>38569</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8160</v>
+        <v>8165</v>
       </c>
       <c r="AT38" s="6">
-        <v>38896</v>
+        <v>38901</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.008478311597397</v>
+        <v>1.008607949389406</v>
       </c>
       <c r="AV38" s="7">
         <v>25488</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5641</v>
+        <v>5644</v>
       </c>
       <c r="AY38" s="6">
-        <v>25696</v>
+        <v>25699</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0081607030759574</v>
+        <v>1.0082784055241683</v>
       </c>
       <c r="BA38" s="7">
         <v>25933</v>
@@ -7561,14 +7561,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5617</v>
+        <v>5619</v>
       </c>
       <c r="BD38" s="6">
-        <v>25965</v>
+        <v>25967</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0012339490224811</v>
+        <v>1.0013110708363862</v>
       </c>
       <c r="BF38" s="7">
         <v>39379</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>11625</v>
+        <v>11632</v>
       </c>
       <c r="BI38" s="6">
-        <v>39528</v>
+        <v>39535</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.003783742603926</v>
+        <v>1.0039615023235735</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>64470</v>
+        <v>64481</v>
       </c>
       <c r="F40" s="13">
-        <v>289199</v>
+        <v>289210</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99058393960568325</v>
+        <v>0.99062161754833056</v>
       </c>
       <c r="H40" s="7">
         <v>293812</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>59785</v>
+        <v>59795</v>
       </c>
       <c r="K40" s="13">
-        <v>290818</v>
+        <v>290828</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98980981035492088</v>
+        <v>0.98984384572447692</v>
       </c>
       <c r="M40" s="7">
         <v>351809</v>
@@ -7849,14 +7849,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>72192</v>
+        <v>72207</v>
       </c>
       <c r="P40" s="6">
-        <v>349230</v>
+        <v>349245</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.9926693177263799</v>
+        <v>0.99271195449803729</v>
       </c>
       <c r="R40" s="7">
         <v>293831</v>
@@ -7866,14 +7866,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>63261</v>
+        <v>63274</v>
       </c>
       <c r="U40" s="13">
-        <v>292869</v>
+        <v>292882</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99672600916853571</v>
+        <v>0.99677025228787974</v>
       </c>
       <c r="W40" s="7">
         <v>297227</v>
@@ -7883,14 +7883,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>66728</v>
+        <v>66742</v>
       </c>
       <c r="Z40" s="13">
-        <v>294273</v>
+        <v>294287</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.99006146817079199</v>
+        <v>0.99010857021737597</v>
       </c>
       <c r="AB40" s="7">
         <v>355500</v>
@@ -7900,14 +7900,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>82290</v>
+        <v>82309</v>
       </c>
       <c r="AE40" s="6">
-        <v>352841</v>
+        <v>352860</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.99252039381153301</v>
+        <v>0.99257383966244728</v>
       </c>
       <c r="AG40" s="7">
         <v>298328</v>
@@ -7917,14 +7917,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>79527</v>
+        <v>79542</v>
       </c>
       <c r="AJ40" s="6">
-        <v>295999</v>
+        <v>296014</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99219315652570328</v>
+        <v>0.99224343675417659</v>
       </c>
       <c r="AL40" s="7">
         <v>299711</v>
@@ -7934,14 +7934,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>69592</v>
+        <v>69613</v>
       </c>
       <c r="AO40" s="6">
-        <v>297223</v>
+        <v>297244</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99169866971849552</v>
+        <v>0.99176873721685221</v>
       </c>
       <c r="AQ40" s="7">
         <v>357015</v>
@@ -7951,14 +7951,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>77018</v>
+        <v>77048</v>
       </c>
       <c r="AT40" s="6">
-        <v>355215</v>
+        <v>355245</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.9949581950338221</v>
+        <v>0.99504222511659179</v>
       </c>
       <c r="AV40" s="7">
         <v>300800</v>
@@ -7968,14 +7968,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>66714</v>
+        <v>66740</v>
       </c>
       <c r="AY40" s="6">
-        <v>299414</v>
+        <v>299440</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99539228723404261</v>
+        <v>0.99547872340425536</v>
       </c>
       <c r="BA40" s="7">
         <v>303731</v>
@@ -7985,14 +7985,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>65514</v>
+        <v>65547</v>
       </c>
       <c r="BD40" s="6">
-        <v>300751</v>
+        <v>300784</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.99018868669974414</v>
+        <v>0.99029733547118992</v>
       </c>
       <c r="BF40" s="7">
         <v>361393</v>
@@ -8002,14 +8002,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>110732</v>
+        <v>110782</v>
       </c>
       <c r="BI40" s="6">
-        <v>358539</v>
+        <v>358589</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99210278007598374</v>
+        <v>0.99224113361354538</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>153102</v>
+        <v>153138</v>
       </c>
       <c r="F41" s="13">
-        <v>944427</v>
+        <v>944463</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99162018798666118</v>
+        <v>0.99165798691317164</v>
       </c>
       <c r="H41" s="7">
         <v>959446</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>141566</v>
+        <v>141604</v>
       </c>
       <c r="K41" s="13">
-        <v>948100</v>
+        <v>948138</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.98817442565814018</v>
+        <v>0.9882140318475453</v>
       </c>
       <c r="M41" s="7">
         <v>1062442</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>158505</v>
+        <v>158549</v>
       </c>
       <c r="P41" s="6">
-        <v>1051986</v>
+        <v>1052030</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99015852159459061</v>
+        <v>0.99019993562001507</v>
       </c>
       <c r="R41" s="7">
         <v>959218</v>
@@ -8078,14 +8078,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>144720</v>
+        <v>144763</v>
       </c>
       <c r="U41" s="13">
-        <v>951610</v>
+        <v>951653</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.99206853916419413</v>
+        <v>0.9921133673471515</v>
       </c>
       <c r="W41" s="7">
         <v>961845</v>
@@ -8095,14 +8095,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>150998</v>
+        <v>151049</v>
       </c>
       <c r="Z41" s="13">
-        <v>950605</v>
+        <v>950656</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.98831412545680442</v>
+        <v>0.98836714855304131</v>
       </c>
       <c r="AB41" s="7">
         <v>1065577</v>
@@ -8112,14 +8112,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>183933</v>
+        <v>183985</v>
       </c>
       <c r="AE41" s="6">
-        <v>1055228</v>
+        <v>1055280</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99028789097362269</v>
+        <v>0.99033669082572162</v>
       </c>
       <c r="AG41" s="7">
         <v>963364</v>
@@ -8129,14 +8129,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>171259</v>
+        <v>171313</v>
       </c>
       <c r="AJ41" s="6">
-        <v>956602</v>
+        <v>956656</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.99298084628447814</v>
+        <v>0.99303689986339538</v>
       </c>
       <c r="AL41" s="7">
         <v>968650</v>
@@ -8146,14 +8146,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>149873</v>
+        <v>149929</v>
       </c>
       <c r="AO41" s="6">
-        <v>959106</v>
+        <v>959162</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.9901471119599442</v>
+        <v>0.99020492437929075</v>
       </c>
       <c r="AQ41" s="7">
         <v>1071657</v>
@@ -8163,14 +8163,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>157113</v>
+        <v>157174</v>
       </c>
       <c r="AT41" s="6">
-        <v>1063518</v>
+        <v>1063579</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99240521920726499</v>
+        <v>0.99246214040499903</v>
       </c>
       <c r="AV41" s="7">
         <v>970535</v>
@@ -8180,14 +8180,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>145073</v>
+        <v>145136</v>
       </c>
       <c r="AY41" s="6">
-        <v>964682</v>
+        <v>964745</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99396930558918539</v>
+        <v>0.99403421824045501</v>
       </c>
       <c r="BA41" s="7">
         <v>973311</v>
@@ -8197,14 +8197,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>140806</v>
+        <v>140893</v>
       </c>
       <c r="BD41" s="6">
-        <v>969378</v>
+        <v>969465</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.99595915385729739</v>
+        <v>0.99604853946991245</v>
       </c>
       <c r="BF41" s="7">
         <v>1078355</v>
@@ -8214,14 +8214,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>223499</v>
+        <v>223598</v>
       </c>
       <c r="BI41" s="6">
-        <v>1074326</v>
+        <v>1074425</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99626375358764041</v>
+        <v>0.99635556008921</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8273,14 +8273,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="P42" s="6">
-        <v>20997</v>
+        <v>20998</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99065817409766455</v>
+        <v>0.99070535503656521</v>
       </c>
       <c r="R42" s="7">
         <v>19210</v>
@@ -8409,14 +8409,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="BD42" s="6">
-        <v>19428</v>
+        <v>19429</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.9876467896904072</v>
+        <v>0.98769762594682531</v>
       </c>
       <c r="BF42" s="7">
         <v>21792</v>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>5299</v>
+        <v>5301</v>
       </c>
       <c r="BI42" s="6">
-        <v>21596</v>
+        <v>21598</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.99100587371512483</v>
+        <v>0.99109765051395005</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8451,14 +8451,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="24"/>
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F43" s="13">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="25"/>
-        <v>1.0008176614881439</v>
+        <v>1.0010902153175252</v>
       </c>
       <c r="H43" s="7">
         <v>3731</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K43" s="13">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99329938354328595</v>
+        <v>0.99356740820155454</v>
       </c>
       <c r="M43" s="7">
         <v>4602</v>
@@ -8485,14 +8485,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="P43" s="6">
-        <v>4592</v>
+        <v>4593</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99782703172533682</v>
+        <v>0.99804432855280312</v>
       </c>
       <c r="R43" s="7">
         <v>3744</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="30"/>
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="U43" s="13">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="31"/>
-        <v>0.99813034188034189</v>
+        <v>0.9983974358974359</v>
       </c>
       <c r="W43" s="7">
         <v>3795</v>
@@ -8519,14 +8519,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="Z43" s="13">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.99077733860342554</v>
+        <v>0.99104084321475627</v>
       </c>
       <c r="AB43" s="7">
         <v>4656</v>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="AE43" s="6">
-        <v>4632</v>
+        <v>4634</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99484536082474229</v>
+        <v>0.9952749140893471</v>
       </c>
       <c r="AG43" s="7">
         <v>3765</v>
@@ -8553,14 +8553,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="12"/>
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="AJ43" s="6">
-        <v>3774</v>
+        <v>3776</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="36"/>
-        <v>1.0023904382470119</v>
+        <v>1.002921646746348</v>
       </c>
       <c r="AL43" s="7">
         <v>3815</v>
@@ -8570,14 +8570,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="37"/>
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="AO43" s="6">
-        <v>3812</v>
+        <v>3814</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="38"/>
-        <v>0.99921363040629096</v>
+        <v>0.99973787680209703</v>
       </c>
       <c r="AQ43" s="7">
         <v>4752</v>
@@ -8587,14 +8587,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="39"/>
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="AT43" s="6">
-        <v>4761</v>
+        <v>4763</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="40"/>
-        <v>1.0018939393939394</v>
+        <v>1.0023148148148149</v>
       </c>
       <c r="AV43" s="7">
         <v>3858</v>
@@ -8604,14 +8604,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="41"/>
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="AY43" s="6">
-        <v>3833</v>
+        <v>3835</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="42"/>
-        <v>0.99351995852773456</v>
+        <v>0.99403836184551586</v>
       </c>
       <c r="BA43" s="7">
         <v>3902</v>
@@ -8621,14 +8621,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="BD43" s="6">
-        <v>3868</v>
+        <v>3872</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.99128651973347004</v>
+        <v>0.99231163505894415</v>
       </c>
       <c r="BF43" s="7">
         <v>4852</v>
@@ -8638,14 +8638,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="BI43" s="6">
-        <v>4811</v>
+        <v>4813</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.99154987633965375</v>
+        <v>0.99196207749381693</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>82004</v>
+        <v>82010</v>
       </c>
       <c r="F44" s="13">
-        <v>359491</v>
+        <v>359497</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98837292422742773</v>
+        <v>0.98838942043330036</v>
       </c>
       <c r="H44" s="7">
         <v>368428</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>72525</v>
+        <v>72528</v>
       </c>
       <c r="K44" s="13">
-        <v>362244</v>
+        <v>362247</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98321517365672528</v>
+        <v>0.98322331636032001</v>
       </c>
       <c r="M44" s="7">
         <v>437654</v>
@@ -8697,14 +8697,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>87139</v>
+        <v>87149</v>
       </c>
       <c r="P44" s="6">
-        <v>430605</v>
+        <v>430615</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.98389366942836121</v>
+        <v>0.98391651852833517</v>
       </c>
       <c r="R44" s="7">
         <v>368991</v>
@@ -8714,14 +8714,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>80941</v>
+        <v>80947</v>
       </c>
       <c r="U44" s="13">
-        <v>364691</v>
+        <v>364697</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.98834659923954782</v>
+        <v>0.98836285979874849</v>
       </c>
       <c r="W44" s="7">
         <v>375659</v>
@@ -8731,14 +8731,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>79230</v>
+        <v>79241</v>
       </c>
       <c r="Z44" s="13">
-        <v>364729</v>
+        <v>364740</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.97090446388879281</v>
+        <v>0.97093374576411051</v>
       </c>
       <c r="AB44" s="7">
         <v>443838</v>
@@ -8748,14 +8748,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>99906</v>
+        <v>99922</v>
       </c>
       <c r="AE44" s="6">
-        <v>433665</v>
+        <v>433681</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.97707947494356051</v>
+        <v>0.97711552413267899</v>
       </c>
       <c r="AG44" s="7">
         <v>373881</v>
@@ -8765,14 +8765,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>83396</v>
+        <v>83408</v>
       </c>
       <c r="AJ44" s="6">
-        <v>366858</v>
+        <v>366870</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.98121594838999571</v>
+        <v>0.98124804416378475</v>
       </c>
       <c r="AL44" s="7">
         <v>377474</v>
@@ -8782,14 +8782,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>74601</v>
+        <v>74616</v>
       </c>
       <c r="AO44" s="6">
-        <v>370069</v>
+        <v>370084</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98038275483874382</v>
+        <v>0.98042249267499215</v>
       </c>
       <c r="AQ44" s="7">
         <v>447335</v>
@@ -8799,14 +8799,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>79875</v>
+        <v>79896</v>
       </c>
       <c r="AT44" s="6">
-        <v>440486</v>
+        <v>440507</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.98468932679088383</v>
+        <v>0.98473627147439835</v>
       </c>
       <c r="AV44" s="7">
         <v>379419</v>
@@ -8816,14 +8816,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>74590</v>
+        <v>74610</v>
       </c>
       <c r="AY44" s="6">
-        <v>374428</v>
+        <v>374448</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98684567720646565</v>
+        <v>0.98689838937955132</v>
       </c>
       <c r="BA44" s="7">
         <v>384239</v>
@@ -8833,14 +8833,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>73270</v>
+        <v>73293</v>
       </c>
       <c r="BD44" s="6">
-        <v>377180</v>
+        <v>377203</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98162862176926335</v>
+        <v>0.9816884803468674</v>
       </c>
       <c r="BF44" s="7">
         <v>454173</v>
@@ -8850,14 +8850,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>118537</v>
+        <v>118569</v>
       </c>
       <c r="BI44" s="6">
-        <v>448000</v>
+        <v>448032</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98640826293064532</v>
+        <v>0.98647872066371189</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8875,14 +8875,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>56617</v>
+        <v>56625</v>
       </c>
       <c r="F45" s="13">
-        <v>262436</v>
+        <v>262444</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.98429987022826326</v>
+        <v>0.98432987525410509</v>
       </c>
       <c r="H45" s="7">
         <v>269495</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>50204</v>
+        <v>50214</v>
       </c>
       <c r="K45" s="13">
-        <v>263770</v>
+        <v>263780</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.97875656320154358</v>
+        <v>0.97879366964136627</v>
       </c>
       <c r="M45" s="7">
         <v>320759</v>
@@ -8909,14 +8909,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>60853</v>
+        <v>60866</v>
       </c>
       <c r="P45" s="6">
-        <v>314775</v>
+        <v>314788</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.9813442491091442</v>
+        <v>0.98138477797972934</v>
       </c>
       <c r="R45" s="7">
         <v>267358</v>
@@ -8926,14 +8926,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>51934</v>
+        <v>51943</v>
       </c>
       <c r="U45" s="13">
-        <v>263986</v>
+        <v>263995</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.98738769739450472</v>
+        <v>0.98742136012387882</v>
       </c>
       <c r="W45" s="7">
         <v>269851</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>56929</v>
+        <v>56940</v>
       </c>
       <c r="Z45" s="13">
-        <v>263933</v>
+        <v>263944</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.97806937902768565</v>
+        <v>0.97811014226369364</v>
       </c>
       <c r="AB45" s="7">
         <v>321990</v>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>71984</v>
+        <v>71996</v>
       </c>
       <c r="AE45" s="6">
-        <v>316391</v>
+        <v>316403</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98261126121929254</v>
+        <v>0.98264852945743653</v>
       </c>
       <c r="AG45" s="7">
         <v>270238</v>
@@ -8977,14 +8977,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>57429</v>
+        <v>57443</v>
       </c>
       <c r="AJ45" s="6">
-        <v>266690</v>
+        <v>266704</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98687083237738582</v>
+        <v>0.98692263856304441</v>
       </c>
       <c r="AL45" s="7">
         <v>273027</v>
@@ -8994,14 +8994,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>52485</v>
+        <v>52498</v>
       </c>
       <c r="AO45" s="6">
-        <v>269442</v>
+        <v>269455</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98686943049588505</v>
+        <v>0.98691704483439369</v>
       </c>
       <c r="AQ45" s="7">
         <v>326184</v>
@@ -9011,14 +9011,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>60872</v>
+        <v>60889</v>
       </c>
       <c r="AT45" s="6">
-        <v>323009</v>
+        <v>323026</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.99026623010325465</v>
+        <v>0.99031834792632378</v>
       </c>
       <c r="AV45" s="7">
         <v>274208</v>
@@ -9028,14 +9028,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>52522</v>
+        <v>52539</v>
       </c>
       <c r="AY45" s="6">
-        <v>272460</v>
+        <v>272477</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.99362527716186255</v>
+        <v>0.99368727389427003</v>
       </c>
       <c r="BA45" s="7">
         <v>277741</v>
@@ -9045,14 +9045,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>50396</v>
+        <v>50413</v>
       </c>
       <c r="BD45" s="6">
-        <v>274791</v>
+        <v>274808</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98937859372580927</v>
+        <v>0.98943980182976221</v>
       </c>
       <c r="BF45" s="7">
         <v>331328</v>
@@ -9062,14 +9062,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>87302</v>
+        <v>87332</v>
       </c>
       <c r="BI45" s="6">
-        <v>329181</v>
+        <v>329211</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.9935200164187753</v>
+        <v>0.99361056113579294</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F46" s="13">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.023534269199009</v>
+        <v>1.0239471511147811</v>
       </c>
       <c r="H46" s="7">
         <v>2553</v>
@@ -9104,14 +9104,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K46" s="13">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0011750881316099</v>
+        <v>1.0015667841754798</v>
       </c>
       <c r="M46" s="7">
         <v>7561</v>
@@ -9121,14 +9121,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="P46" s="6">
-        <v>7680</v>
+        <v>7681</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0157386589075519</v>
+        <v>1.0158709165454305</v>
       </c>
       <c r="R46" s="7">
         <v>2328</v>
@@ -9138,14 +9138,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="U46" s="13">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.0274914089347078</v>
+        <v>1.0279209621993126</v>
       </c>
       <c r="W46" s="7">
         <v>2515</v>
@@ -9155,14 +9155,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Z46" s="13">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98489065606361825</v>
+        <v>0.98528827037773359</v>
       </c>
       <c r="AB46" s="7">
         <v>7764</v>
@@ -9172,14 +9172,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="AE46" s="6">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.0179031427099434</v>
+        <v>1.0180319422977846</v>
       </c>
       <c r="AG46" s="7">
         <v>2401</v>
@@ -9189,14 +9189,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="12"/>
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AJ46" s="6">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="36"/>
-        <v>1.0295710120783008</v>
+        <v>1.029987505206164</v>
       </c>
       <c r="AL46" s="7">
         <v>2561</v>
@@ -9206,14 +9206,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AO46" s="6">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>1.0011714174150723</v>
+        <v>1.0015618898867631</v>
       </c>
       <c r="AQ46" s="7">
         <v>7981</v>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="AT46" s="6">
-        <v>8150</v>
+        <v>8151</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0211752913168777</v>
+        <v>1.0213005888986342</v>
       </c>
       <c r="AV46" s="7">
         <v>2437</v>
@@ -9240,14 +9240,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AY46" s="6">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.0311858842839556</v>
+        <v>1.0315962248666393</v>
       </c>
       <c r="BA46" s="7">
         <v>2592</v>
@@ -9257,14 +9257,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="BD46" s="6">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>0.99421296296296291</v>
+        <v>0.9945987654320988</v>
       </c>
       <c r="BF46" s="7">
         <v>8179</v>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="BI46" s="6">
-        <v>8328</v>
+        <v>8329</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0182173859885071</v>
+        <v>1.0183396503240005</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9511,15 +9511,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1531931</v>
+        <v>1532258</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8130824</v>
+        <v>8131151</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99118531799805243</v>
+        <v>0.99122518082117905</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9531,15 +9531,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1394484</v>
+        <v>1394831</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8217403</v>
+        <v>8217750</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.96605546111397178</v>
+        <v>0.9660962551756731</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9551,15 +9551,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2225857</v>
+        <v>2226433</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>12636111</v>
+        <v>12636687</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99124805317486053</v>
+        <v>0.99129323787437995</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9571,15 +9571,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1485202</v>
+        <v>1485608</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8215783</v>
+        <v>8216189</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.9942434975834864</v>
+        <v>0.99429263019324732</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9591,15 +9591,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1503456</v>
+        <v>1503924</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8256083</v>
+        <v>8256551</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98107690883550935</v>
+        <v>0.98113252164770304</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9611,15 +9611,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2453729</v>
+        <v>2454553</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>12734189</v>
+        <v>12735013</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.98950606088721027</v>
+        <v>0.98957008954220915</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9631,15 +9631,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" ref="AI48" si="47">AJ48-AH48</f>
-        <v>1730557</v>
+        <v>1731120</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8291895</v>
+        <v>8292458</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" ref="AK48" si="48">AJ48/AG48</f>
-        <v>0.99247305225594784</v>
+        <v>0.99254043882179555</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9651,15 +9651,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="37"/>
-        <v>1400179</v>
+        <v>1400803</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>8367665</v>
+        <v>8368289</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="38"/>
-        <v>0.98606107742798388</v>
+        <v>0.98613461073892728</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9671,15 +9671,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="39"/>
-        <v>2054718</v>
+        <v>2055856</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>12913512</v>
+        <v>12914650</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="40"/>
-        <v>0.9936274327248642</v>
+        <v>0.9937149958926873</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9691,15 +9691,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="41"/>
-        <v>1421237</v>
+        <v>1421970</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>8449708</v>
+        <v>8450441</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="42"/>
-        <v>0.99639105301891573</v>
+        <v>0.9964774885077945</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9711,15 +9711,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="43"/>
-        <v>1411440</v>
+        <v>1412316</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>8541494</v>
+        <v>8542370</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="44"/>
-        <v>0.98807392831817353</v>
+        <v>0.98817526337281469</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="45"/>
-        <v>2972095</v>
+        <v>2973848</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13130713</v>
+        <v>13132466</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="46"/>
-        <v>0.99409653796099384</v>
+        <v>0.99422925362015457</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
